--- a/data/xlsx/ceidg.xlsx
+++ b/data/xlsx/ceidg.xlsx
@@ -205,7 +205,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>magdalena.pawlak@astra-finance.pl</t>
+          <t>magdalena.pawlak@interia.pl</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>r.michalski@biuro.pl</t>
+          <t>r.michalski@o2.pl</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>krol.agnieszka@poczta.pl</t>
+          <t>krol.agnieszka@brak-domeny</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>wojciechwieczorek@mail.pl</t>
+          <t>wojciechwieczorek@outlook.com</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>justyna_jablonska@nova-data.pl</t>
+          <t>justyna_jablonska@yahoo.com</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>piotr.witkowski95@wp.pl</t>
+          <t>piotr.witkowski95@icloud.com</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>m.stepien@proton.me</t>
+          <t>m.stepien@localhost</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>baran.joanna@silesia-invest.pl</t>
+          <t>baran.joanna@onet.pl</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>pawelrutkowski@poczta.pl</t>
+          <t>pawelrutkowski@interia.pl</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>magdalena_gorska@mail.pl</t>
+          <t>magdalena_gorska@o2.pl</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>robert.sikora72@onet.pl</t>
+          <t>robert.sikora72@proton.me</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>agnieszka.ostrowska@helios-markets.pl</t>
+          <t>agnieszka.ostrowska@brak-domeny</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>w.tomaszewski@gmail.com</t>
+          <t>w.tomaszewski@yahoo.com</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>zajac.justyna@proton.me</t>
+          <t>zajac.justyna@icloud.com</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>piotrpietrzak@biuro.pl</t>
+          <t>piotrpietrzak@gmail.com</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>maria_wojcicka@polaris-capital.pl</t>
+          <t>maria_wojcicka@wp.pl</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>michal.czarnecki78@mail.pl</t>
+          <t>michal.czarnecki78@localhost</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>joanna.lis@onet.pl</t>
+          <t>joanna.lis@interia.pl</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>p.kolodziej@wp.pl</t>
+          <t>p.kolodziej@o2.pl</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>kaczmarek.magdalena@astra-finance.pl</t>
+          <t>kaczmarek.magdalena@proton.me</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>robertpiatek@proton.me</t>
+          <t>robertpiatek@outlook.com</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>agnieszka_sadowska@biuro.pl</t>
+          <t>agnieszka_sadowska@brak-domeny</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>wojciech.wlodarczyk84@poczta.pl</t>
+          <t>wojciech.wlodarczyk84@icloud.com</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>justyna.borkowska@nova-data.pl</t>
+          <t>justyna.borkowska@gmail.com</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>p.kowalski@onet.pl</t>
+          <t>p.kowalski@wp.pl</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>nowacka.maria@wp.pl</t>
+          <t>nowacka.maria@onet.pl</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>joanna_wojcik@silesia-invest.pl</t>
+          <t>joanna_wojcik@localhost</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>pawel.kowalczyk90@biuro.pl</t>
+          <t>pawel.kowalczyk90@o2.pl</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>magdalena.kaminska@poczta.pl</t>
+          <t>magdalena.kaminska@proton.me</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>r.lewandowski@mail.pl</t>
+          <t>r.lewandowski@outlook.com</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>zielinska.agnieszka@helios-markets.pl</t>
+          <t>zielinska.agnieszka@yahoo.com</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>wojciechszymanski@wp.pl</t>
+          <t>wojciechszymanski@brak-domeny</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>piotr.mazur96@proton.me</t>
+          <t>piotr.mazur96@wp.pl</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>maria.krawczyk@polaris-capital.pl</t>
+          <t>maria.krawczyk@onet.pl</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>m.wozniak@poczta.pl</t>
+          <t>m.wozniak@interia.pl</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>jankowska.joanna@mail.pl</t>
+          <t>jankowska.joanna@localhost</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>pawelgrabowski@onet.pl</t>
+          <t>pawelgrabowski@proton.me</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>magdalena_pawlak@astra-finance.pl</t>
+          <t>magdalena_pawlak@outlook.com</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>robert.michalski73@gmail.com</t>
+          <t>robert.michalski73@yahoo.com</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>agnieszka.krol@proton.me</t>
+          <t>agnieszka.krol@icloud.com</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>w.wieczorek@biuro.pl</t>
+          <t>w.wieczorek@brak-domeny</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>jablonska.justyna@nova-data.pl</t>
+          <t>jablonska.justyna@wp.pl</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>piotrwitkowski@mail.pl</t>
+          <t>piotrwitkowski@onet.pl</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>maria_walczak@onet.pl</t>
+          <t>maria_walczak@interia.pl</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>michal.stepien79@wp.pl</t>
+          <t>michal.stepien79@o2.pl</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>joanna.baran@silesia-invest.pl</t>
+          <t>joanna.baran@localhost</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>p.rutkowski@proton.me</t>
+          <t>p.rutkowski@outlook.com</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>gorska.magdalena@biuro.pl</t>
+          <t>gorska.magdalena@yahoo.com</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>robertsikora@poczta.pl</t>
+          <t>robertsikora@icloud.com</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>agnieszka_ostrowska@helios-markets.pl</t>
+          <t>agnieszka_ostrowska@gmail.com</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>wojciech.tomaszewski85@onet.pl</t>
+          <t>wojciech.tomaszewski85@wp.pl</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>justyna.zajac@wp.pl</t>
+          <t>justyna.zajac@domena..pl</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>p.pietrzak@gmail.com</t>
+          <t>p.pietrzak@interia.pl</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>wojcicka.maria@polaris-capital.pl</t>
+          <t>wojcicka.maria@o2.pl</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>michalczarnecki@biuro.pl</t>
+          <t>michalczarnecki@proton.me</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>joanna_lis@poczta.pl</t>
+          <t>joanna_lis@outlook.com</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>pawel.kolodziej91@mail.pl</t>
+          <t>pawel.kolodziej91@.pl</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>magdalena.kaczmarek@astra-finance.pl</t>
+          <t>magdalena.kaczmarek@icloud.com</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>r.piatek@wp.pl</t>
+          <t>r.piatek@gmail.com</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>sadowska.agnieszka@gmail.com</t>
+          <t>sadowska.agnieszka@wp.pl</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>wojciechwlodarczyk@proton.me</t>
+          <t>wojciechwlodarczyk@onet.pl</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>justyna_borkowska@nova-data.pl</t>
+          <t>justyna_borkowska@domena..pl</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>piotr.kowalski97@poczta.pl</t>
+          <t>piotr.kowalski97@o2.pl</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>maria.nowacka@mail.pl</t>
+          <t>maria.nowacka@proton.me</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>m.wisniewski@onet.pl</t>
+          <t>m.wisniewski@outlook.com</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>wojcik.joanna@silesia-invest.pl</t>
+          <t>wojcik.joanna@yahoo.com</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>pawelkowalczyk@gmail.com</t>
+          <t>pawelkowalczyk@.pl</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>magdalena_kaminska@proton.me</t>
+          <t>magdalena_kaminska@gmail.com</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>robert.lewandowski74@biuro.pl</t>
+          <t>robert.lewandowski74@wp.pl</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>agnieszka.zielinska@helios-markets.pl</t>
+          <t>agnieszka.zielinska@onet.pl</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>w.szymanski@mail.pl</t>
+          <t>w.szymanski@interia.pl</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>dabrowska.justyna@onet.pl</t>
+          <t>dabrowska.justyna@domena..pl</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>piotrmazur@wp.pl</t>
+          <t>piotrmazur@proton.me</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>maria_krawczyk@polaris-capital.pl</t>
+          <t>maria_krawczyk@outlook.com</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>michal.wozniak80@proton.me</t>
+          <t>michal.wozniak80@yahoo.com</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>joanna.jankowska@biuro.pl</t>
+          <t>joanna.jankowska@icloud.com</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>p.grabowski@poczta.pl</t>
+          <t>p.grabowski@.pl</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>pawlak.magdalena@astra-finance.pl</t>
+          <t>pawlak.magdalena@wp.pl</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>wojciech.wieczorek86@gmail.com</t>
+          <t>wojciech.wieczorek86@interia.pl</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>justyna.jablonska@nova-data.pl</t>
+          <t>justyna.jablonska@o2.pl</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>p.witkowski@biuro.pl</t>
+          <t>p.witkowski@domena..pl</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>walczak.maria@poczta.pl</t>
+          <t>walczak.maria@outlook.com</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>michalstepien@mail.pl</t>
+          <t>michalstepien@yahoo.com</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>joanna_baran@silesia-invest.pl</t>
+          <t>joanna_baran@icloud.com</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>pawel.rutkowski92@wp.pl</t>
+          <t>pawel.rutkowski92@gmail.com</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>magdalena.gorska@gmail.com</t>
+          <t>magdalena.gorska@.pl</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>r.sikora@proton.me</t>
+          <t>r.sikora@onet.pl</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>ostrowska.agnieszka@helios-markets.pl</t>
+          <t>ostrowska.agnieszka@interia.pl</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>wojciechtomaszewski@poczta.pl</t>
+          <t>wojciechtomaszewski@o2.pl</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>justyna_zajac@mail.pl</t>
+          <t>justyna_zajac@proton.me</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>piotr.pietrzak98@onet.pl</t>
+          <t>piotr.pietrzak98@domena..pl</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>maria.wojcicka@polaris-capital.pl</t>
+          <t>maria.wojcicka@yahoo.com</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>m.czarnecki@gmail.com</t>
+          <t>m.czarnecki@icloud.com</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>lis.joanna@proton.me</t>
+          <t>lis.joanna@gmail.com</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>pawelkolodziej@biuro.pl</t>
+          <t>pawelkolodziej@wp.pl</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>magdalena_kaczmarek@astra-finance.pl</t>
+          <t>magdalena_kaczmarek@.pl</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>robert.piatek75@mail.pl</t>
+          <t>robert.piatek75@interia.pl</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>agnieszka.sadowska@onet.pl</t>
+          <t>agnieszka.sadowska@o2.pl</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>w.wlodarczyk@wp.pl</t>
+          <t>w.wlodarczyk@proton.me</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>borkowska.justyna@nova-data.pl</t>
+          <t>borkowska.justyna@outlook.com</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>piotrkowalski@proton.me</t>
+          <t>piotrkowalski@domena..pl</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>maria_nowacka@biuro.pl</t>
+          <t>maria_nowacka@icloud.com</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>michal.wisniewski81@poczta.pl</t>
+          <t>michal.wisniewski81@gmail.com</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>joanna.wojcik@silesia-invest.pl</t>
+          <t>joanna.wojcik@wp.pl</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>kaminska.magdalena@wp.pl</t>
+          <t>kaminska.magdalena@.pl</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>robertlewandowski@gmail.com</t>
+          <t>robertlewandowski@o2.pl</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>agnieszka_zielinska@helios-markets.pl</t>
+          <t>agnieszka_zielinska@proton.me</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>wojciech.szymanski87@biuro.pl</t>
+          <t>wojciech.szymanski87@outlook.com</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>justyna.dabrowska@poczta.pl</t>
+          <t>justyna.dabrowska@yahoo.com</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>p.mazur@mail.pl</t>
+          <t>p.mazur@domena..pl</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>krawczyk.maria@polaris-capital.pl</t>
+          <t>krawczyk.maria@gmail.com</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>joanna_jankowska@gmail.com</t>
+          <t>joanna_jankowska@onet.pl</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>pawel.grabowski93@proton.me</t>
+          <t>pawel.grabowski93@interia.pl</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>magdalena.pawlak@astra-finance.pl</t>
+          <t>magdalena.pawlak@.pl</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>r.michalski@poczta.pl</t>
+          <t>r.michalski@proton.me</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>krol.agnieszka@mail.pl</t>
+          <t>krol.agnieszka@outlook.com</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>wojciechwieczorek@onet.pl</t>
+          <t>wojciechwieczorek@yahoo.com</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>justyna_jablonska@nova-data.pl</t>
+          <t>justyna_jablonska@icloud.com</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>piotr.witkowski70@gmail.com</t>
+          <t>piotr.witkowski70@domena..pl</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>maria.walczak@proton.me</t>
+          <t>maria.walczak@wp.pl</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>baran.joanna@silesia-invest.pl</t>
+          <t>baran.joanna@onet.pl</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>pawelrutkowski@mail.pl</t>
+          <t>pawelrutkowski@interia.pl</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>magdalena_gorska@onet.pl</t>
+          <t>magdalena_gorska@o2.pl</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>robert.sikora76@wp.pl</t>
+          <t>robert.sikora76@.pl</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>agnieszka.ostrowska@helios-markets.pl</t>
+          <t>agnieszka.ostrowska@outlook.com</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>w.tomaszewski@proton.me</t>
+          <t>w.tomaszewski@yahoo.com</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>zajac.justyna@biuro.pl</t>
+          <t>zajac.justyna@icloud.com</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>piotrpietrzak@poczta.pl</t>
+          <t>piotrpietrzak@gmail.com</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>maria_wojcicka@polaris-capital.pl</t>
+          <t>maria_wojcicka@domena..pl</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>joanna.lis@wp.pl</t>
+          <t>joanna.lis@interia.pl</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>p.kolodziej@gmail.com</t>
+          <t>p.kolodziej@o2.pl</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>kaczmarek.magdalena@astra-finance.pl</t>
+          <t>kaczmarek.magdalena@proton.me</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>robertpiatek@biuro.pl</t>
+          <t>robertpiatek@.pl</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>agnieszka_sadowska@poczta.pl</t>
+          <t>agnieszka_sadowska@yahoo.com</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>wojciech.wlodarczyk88@mail.pl</t>
+          <t>wojciech.wlodarczyk88@icloud.com</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>justyna.borkowska@nova-data.pl</t>
+          <t>justyna.borkowska@gmail.com</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>nowacka.maria@gmail.com</t>
+          <t>nowacka.maria@domena..pl</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>michalwisniewski@proton.me</t>
+          <t>michalwisniewski@interia.pl</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>joanna_wojcik@silesia-invest.pl</t>
+          <t>joanna_wojcik@o2.pl</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>pawel.kowalczyk94@poczta.pl</t>
+          <t>pawel.kowalczyk94@proton.me</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>magdalena.kaminska@mail.pl</t>
+          <t>magdalena.kaminska@outlook.com</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>r.lewandowski@onet.pl</t>
+          <t>r.lewandowski@yahoo.com</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>zielinska.agnieszka@helios-markets.pl</t>
+          <t>zielinska.agnieszka@wp</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>justyna_dabrowska@proton.me</t>
+          <t>justyna_dabrowska@wp.pl</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>piotr.mazur71@biuro.pl</t>
+          <t>piotr.mazur71@onet.pl</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>maria.krawczyk@polaris-capital.pl</t>
+          <t>maria.krawczyk@interia.pl</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>m.wozniak@mail.pl</t>
+          <t>@m.wozniak.invalid</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>jankowska.joanna@onet.pl</t>
+          <t>jankowska.joanna@proton.me</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>pawelgrabowski@wp.pl</t>
+          <t>pawelgrabowski@outlook.com</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>magdalena_pawlak@astra-finance.pl</t>
+          <t>magdalena_pawlak@yahoo.com</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>robert.michalski77@proton.me</t>
+          <t>robert.michalski77@icloud.com</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>agnieszka.krol@biuro.pl</t>
+          <t>agnieszka.krol@wp</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>w.wieczorek@poczta.pl</t>
+          <t>w.wieczorek@wp.pl</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>jablonska.justyna@nova-data.pl</t>
+          <t>jablonska.justyna@onet.pl</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>piotrwitkowski@onet.pl</t>
+          <t>piotrwitkowski@interia.pl</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>maria_walczak@wp.pl</t>
+          <t>maria_walczak@o2.pl</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>michal.stepien83@gmail.com</t>
+          <t>@michal.stepien83.invalid</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>joanna.baran@silesia-invest.pl</t>
+          <t>joanna.baran@outlook.com</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>p.rutkowski@biuro.pl</t>
+          <t>p.rutkowski@yahoo.com</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>gorska.magdalena@poczta.pl</t>
+          <t>gorska.magdalena@icloud.com</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>robertsikora@mail.pl</t>
+          <t>robertsikora@gmail.com</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>agnieszka_ostrowska@helios-markets.pl</t>
+          <t>agnieszka_ostrowska@wp</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>wojciech.tomaszewski89@wp.pl</t>
+          <t>wojciech.tomaszewski89@onet.pl</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>justyna.zajac@gmail.com</t>
+          <t>justyna.zajac@interia.pl</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -16305,7 +16305,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>p.pietrzak@proton.me</t>
+          <t>p.pietrzak@o2.pl</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>wojcicka.maria@polaris-capital.pl</t>
+          <t>wojcicka.maria@proton.me</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>michalczarnecki@poczta.pl</t>
+          <t>@michalczarnecki.invalid</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>joanna_lis@mail.pl</t>
+          <t>joanna_lis@yahoo.com</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>pawel.kolodziej95@onet.pl</t>
+          <t>pawel.kolodziej95@icloud.com</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>magdalena.kaczmarek@astra-finance.pl</t>
+          <t>magdalena.kaczmarek@gmail.com</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>r.piatek@gmail.com</t>
+          <t>r.piatek@wp.pl</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>sadowska.agnieszka@proton.me</t>
+          <t>sadowska.agnieszka@wp</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>wojciechwlodarczyk@biuro.pl</t>
+          <t>wojciechwlodarczyk@interia.pl</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>justyna_borkowska@nova-data.pl</t>
+          <t>justyna_borkowska@o2.pl</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>piotr.kowalski72@mail.pl</t>
+          <t>piotr.kowalski72@proton.me</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>maria.nowacka@onet.pl</t>
+          <t>maria.nowacka@outlook.com</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -17409,7 +17409,7 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>m.wisniewski@wp.pl</t>
+          <t>@m.wisniewski.invalid</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>wojcik.joanna@silesia-invest.pl</t>
+          <t>wojcik.joanna@icloud.com</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>pawelkowalczyk@proton.me</t>
+          <t>pawelkowalczyk@gmail.com</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>magdalena_kaminska@biuro.pl</t>
+          <t>magdalena_kaminska@wp.pl</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>robert.lewandowski78@poczta.pl</t>
+          <t>robert.lewandowski78@onet.pl</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
@@ -17869,7 +17869,7 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>agnieszka.zielinska@helios-markets.pl</t>
+          <t>agnieszka.zielinska@wp</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>w.szymanski@onet.pl</t>
+          <t>w.szymanski@o2.pl</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>dabrowska.justyna@wp.pl</t>
+          <t>dabrowska.justyna@proton.me</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
@@ -18145,7 +18145,7 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>piotrmazur@gmail.com</t>
+          <t>piotrmazur@outlook.com</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>maria_krawczyk@polaris-capital.pl</t>
+          <t>maria_krawczyk@yahoo.com</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>michal.wozniak84@biuro.pl</t>
+          <t>@michal.wozniak84.invalid</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -18421,7 +18421,7 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>joanna.jankowska@poczta.pl</t>
+          <t>joanna.jankowska@gmail.com</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>p.grabowski@mail.pl</t>
+          <t>p.grabowski@wp.pl</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">

--- a/data/xlsx/ceidg.xlsx
+++ b/data/xlsx/ceidg.xlsx
@@ -205,7 +205,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>magdalena.pawlak@interia.pl</t>
+          <t>magdalena.pawlak@tmp.ii</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>r.michalski@o2.pl</t>
+          <t>r.michalski@foo.zz</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>krol.agnieszka@brak-domeny</t>
+          <t>krol.agnieszka@bar.yy</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>wojciechwieczorek@outlook.com</t>
+          <t>wojciechwieczorek@zzz.uu</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>justyna_jablonska@yahoo.com</t>
+          <t>justyna_jablonska@uuu.ii</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>piotr.witkowski95@icloud.com</t>
+          <t>piotr.witkowski95@qqq.zz</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>maria.walczak@gmail.com</t>
+          <t>maria.walczak@abc.yy</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>m.stepien@localhost</t>
+          <t>m.stepien@xxx.uu</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>baran.joanna@onet.pl</t>
+          <t>baran.joanna@interia.pl</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>pawelrutkowski@interia.pl</t>
+          <t>pawelrutkowski@o2.pl</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>magdalena_gorska@o2.pl</t>
+          <t>magdalena_gorska@proton.me</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>robert.sikora72@proton.me</t>
+          <t>robert.sikora72@outlook.com</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>agnieszka.ostrowska@brak-domeny</t>
+          <t>agnieszka.ostrowska@yahoo.com</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>w.tomaszewski@yahoo.com</t>
+          <t>w.tomaszewski@icloud.com</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>zajac.justyna@icloud.com</t>
+          <t>zajac.justyna@gmail.com</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>piotrpietrzak@gmail.com</t>
+          <t>piotrpietrzak@wp.pl</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>maria_wojcicka@wp.pl</t>
+          <t>maria_wojcicka@onet.pl</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>michal.czarnecki78@localhost</t>
+          <t>michal.czarnecki78@interia.pl</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>joanna.lis@interia.pl</t>
+          <t>joanna.lis@o2.pl</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>p.kolodziej@o2.pl</t>
+          <t>p.kolodziej@proton.me</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>kaczmarek.magdalena@proton.me</t>
+          <t>kaczmarek.magdalena@outlook.com</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>robertpiatek@outlook.com</t>
+          <t>robertpiatek@yahoo.com</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>agnieszka_sadowska@brak-domeny</t>
+          <t>agnieszka_sadowska@icloud.com</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>wojciech.wlodarczyk84@icloud.com</t>
+          <t>wojciech.wlodarczyk84@gmail.com</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>justyna.borkowska@gmail.com</t>
+          <t>justyna.borkowska@wp.pl</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>p.kowalski@wp.pl</t>
+          <t>p.kowalski@onet.pl</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>nowacka.maria@onet.pl</t>
+          <t>nowacka.maria@interia.pl</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>michalwisniewski@gmailcom</t>
+          <t>michalwisniewski@o2.pl</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>joanna_wojcik@localhost</t>
+          <t>joanna_wojcik@proton.me</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>pawel.kowalczyk90@o2.pl</t>
+          <t>pawel.kowalczyk90@outlook.com</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>magdalena.kaminska@proton.me</t>
+          <t>magdalena.kaminska@yahoo.com</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>r.lewandowski@outlook.com</t>
+          <t>r.lewandowski@icloud.com</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>zielinska.agnieszka@yahoo.com</t>
+          <t>zielinska.agnieszka@gmail.com</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>wojciechszymanski@brak-domeny</t>
+          <t>wojciechszymanski@wp.pl</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>justyna_dabrowska@gmail.com</t>
+          <t>justyna_dabrowska@onet.pl</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>piotr.mazur96@wp.pl</t>
+          <t>piotr.mazur96@interia.pl</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>maria.krawczyk@onet.pl</t>
+          <t>maria.krawczyk@o2.pl</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>m.wozniak@interia.pl</t>
+          <t>m.wozniak@proton.me</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>jankowska.joanna@localhost</t>
+          <t>jankowska.joanna@outlook.com</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>pawelgrabowski@proton.me</t>
+          <t>pawelgrabowski@yahoo.com</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>magdalena_pawlak@outlook.com</t>
+          <t>magdalena_pawlak@icloud.com</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>robert.michalski73@yahoo.com</t>
+          <t>robert.michalski73@gmail.com</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>agnieszka.krol@icloud.com</t>
+          <t>agnieszka.krol@wp.pl</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>w.wieczorek@brak-domeny</t>
+          <t>w.wieczorek@onet.pl</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>jablonska.justyna@wp.pl</t>
+          <t>jablonska.justyna@interia.pl</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>piotrwitkowski@onet.pl</t>
+          <t>piotrwitkowski@o2.pl</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>maria_walczak@interia.pl</t>
+          <t>maria_walczak@proton.me</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>michal.stepien79@o2.pl</t>
+          <t>michal.stepien79@outlook.com</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>joanna.baran@localhost</t>
+          <t>joanna.baran@yahoo.com</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>p.rutkowski@outlook.com</t>
+          <t>p.rutkowski@icloud.com</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>gorska.magdalena@yahoo.com</t>
+          <t>gorska.magdalena@gmail.com</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>robertsikora@icloud.com</t>
+          <t>robertsikora@wp.pl</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>agnieszka_ostrowska@gmail.com</t>
+          <t>agnieszka_ostrowska@onet.pl</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>wojciech.tomaszewski85@wp.pl</t>
+          <t>wojciech.tomaszewski85@interia.pl</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>justyna.zajac@domena..pl</t>
+          <t>justyna.zajac@o2.pl</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>p.pietrzak@interia.pl</t>
+          <t>p.pietrzak@proton.me</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>wojcicka.maria@o2.pl</t>
+          <t>wojcicka.maria@outlook.com</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>michalczarnecki@proton.me</t>
+          <t>michalczarnecki@yahoo.com</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>joanna_lis@outlook.com</t>
+          <t>joanna_lis@icloud.com</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>pawel.kolodziej91@.pl</t>
+          <t>pawel.kolodziej91@gmail.com</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>magdalena.kaczmarek@icloud.com</t>
+          <t>magdalena.kaczmarek@wp.pl</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>r.piatek@gmail.com</t>
+          <t>r.piatek@onet.pl</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>sadowska.agnieszka@wp.pl</t>
+          <t>sadowska.agnieszka@interia.pl</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>wojciechwlodarczyk@onet.pl</t>
+          <t>wojciechwlodarczyk@o2.pl</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>justyna_borkowska@domena..pl</t>
+          <t>justyna_borkowska@proton.me</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>piotr.kowalski97@o2.pl</t>
+          <t>piotr.kowalski97@outlook.com</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>maria.nowacka@proton.me</t>
+          <t>maria.nowacka@yahoo.com</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>m.wisniewski@outlook.com</t>
+          <t>m.wisniewski@icloud.com</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>wojcik.joanna@yahoo.com</t>
+          <t>wojcik.joanna@gmail.com</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>pawelkowalczyk@.pl</t>
+          <t>pawelkowalczyk@wp.pl</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>magdalena_kaminska@gmail.com</t>
+          <t>magdalena_kaminska@onet.pl</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>robert.lewandowski74@wp.pl</t>
+          <t>robert.lewandowski74@interia.pl</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>agnieszka.zielinska@onet.pl</t>
+          <t>agnieszka.zielinska@o2.pl</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>w.szymanski@interia.pl</t>
+          <t>w.szymanski@proton.me</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>dabrowska.justyna@domena..pl</t>
+          <t>dabrowska.justyna@outlook.com</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>piotrmazur@proton.me</t>
+          <t>piotrmazur@yahoo.com</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>maria_krawczyk@outlook.com</t>
+          <t>maria_krawczyk@icloud.com</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>michal.wozniak80@yahoo.com</t>
+          <t>michal.wozniak80@gmail.com</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>joanna.jankowska@icloud.com</t>
+          <t>joanna.jankowska@wp.pl</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>p.grabowski@.pl</t>
+          <t>p.grabowski@onet.pl</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>pawlak.magdalena@wp.pl</t>
+          <t>pawlak.magdalena@interia.pl</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>robertmichalski@onet.pl</t>
+          <t>robertmichalski@o2.pl</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>wojciech.wieczorek86@interia.pl</t>
+          <t>wojciech.wieczorek86@proton.me</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>justyna.jablonska@o2.pl</t>
+          <t>justyna.jablonska@outlook.com</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>p.witkowski@domena..pl</t>
+          <t>p.witkowski@yahoo.com</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>walczak.maria@outlook.com</t>
+          <t>walczak.maria@icloud.com</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>michalstepien@yahoo.com</t>
+          <t>michalstepien@gmail.com</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>joanna_baran@icloud.com</t>
+          <t>joanna_baran@wp.pl</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>pawel.rutkowski92@gmail.com</t>
+          <t>pawel.rutkowski92@onet.pl</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>magdalena.gorska@.pl</t>
+          <t>magdalena.gorska@interia.pl</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>r.sikora@onet.pl</t>
+          <t>r.sikora@o2.pl</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>ostrowska.agnieszka@interia.pl</t>
+          <t>ostrowska.agnieszka@proton.me</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>wojciechtomaszewski@o2.pl</t>
+          <t>wojciechtomaszewski@outlook.com</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>justyna_zajac@proton.me</t>
+          <t>justyna_zajac@yahoo.com</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>piotr.pietrzak98@domena..pl</t>
+          <t>piotr.pietrzak98@icloud.com</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>maria.wojcicka@yahoo.com</t>
+          <t>maria.wojcicka@gmail.com</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>m.czarnecki@icloud.com</t>
+          <t>m.czarnecki@wp.pl</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>lis.joanna@gmail.com</t>
+          <t>lis.joanna@onet.pl</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>pawelkolodziej@wp.pl</t>
+          <t>pawelkolodziej@interia.pl</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>magdalena_kaczmarek@.pl</t>
+          <t>magdalena_kaczmarek@o2.pl</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>robert.piatek75@interia.pl</t>
+          <t>robert.piatek75@qqq.zz</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>agnieszka.sadowska@o2.pl</t>
+          <t>agnieszka.sadowska@abc.yy</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>w.wlodarczyk@proton.me</t>
+          <t>w.wlodarczyk@xxx.uu</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>borkowska.justyna@outlook.com</t>
+          <t>borkowska.justyna@bbb.ii</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>piotrkowalski@domena..pl</t>
+          <t>piotrkowalski@mmm.zz</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>maria_nowacka@icloud.com</t>
+          <t>maria_nowacka@nnn.yy</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>michal.wisniewski81@gmail.com</t>
+          <t>michal.wisniewski81@kkk.uu</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>joanna.wojcik@wp.pl</t>
+          <t>joanna.wojcik@tmp.ii</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>p.kowalczyk@onet.pl</t>
+          <t>p.kowalczyk@o2.pl</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>kaminska.magdalena@.pl</t>
+          <t>kaminska.magdalena@proton.me</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>robertlewandowski@o2.pl</t>
+          <t>robertlewandowski@outlook.com</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>agnieszka_zielinska@proton.me</t>
+          <t>agnieszka_zielinska@yahoo.com</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>wojciech.szymanski87@outlook.com</t>
+          <t>wojciech.szymanski87@icloud.com</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>justyna.dabrowska@yahoo.com</t>
+          <t>justyna.dabrowska@gmail.com</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>p.mazur@domena..pl</t>
+          <t>p.mazur@wp.pl</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>krawczyk.maria@gmail.com</t>
+          <t>krawczyk.maria@onet.pl</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>michalwozniak@wp.pl</t>
+          <t>michalwozniak@interia.pl</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>joanna_jankowska@onet.pl</t>
+          <t>joanna_jankowska@o2.pl</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>pawel.grabowski93@interia.pl</t>
+          <t>pawel.grabowski93@proton.me</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>magdalena.pawlak@.pl</t>
+          <t>magdalena.pawlak@outlook.com</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>r.michalski@proton.me</t>
+          <t>r.michalski@yahoo.com</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>krol.agnieszka@outlook.com</t>
+          <t>krol.agnieszka@icloud.com</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>wojciechwieczorek@yahoo.com</t>
+          <t>wojciechwieczorek@gmail.com</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>justyna_jablonska@icloud.com</t>
+          <t>justyna_jablonska@wp.pl</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>piotr.witkowski70@domena..pl</t>
+          <t>piotr.witkowski70@onet.pl</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>maria.walczak@wp.pl</t>
+          <t>maria.walczak@interia.pl</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>m.stepienbiuro.pl</t>
+          <t>m.stepienbiuro.pl@o2.pl</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>baran.joanna@onet.pl</t>
+          <t>baran.joanna@proton.me</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>pawelrutkowski@interia.pl</t>
+          <t>pawelrutkowski@outlook.com</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>magdalena_gorska@o2.pl</t>
+          <t>magdalena_gorska@yahoo.com</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>robert.sikora76@.pl</t>
+          <t>robert.sikora76@icloud.com</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>agnieszka.ostrowska@outlook.com</t>
+          <t>agnieszka.ostrowska@gmail.com</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>w.tomaszewski@yahoo.com</t>
+          <t>w.tomaszewski@wp.pl</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>zajac.justyna@icloud.com</t>
+          <t>zajac.justyna@onet.pl</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>piotrpietrzak@gmail.com</t>
+          <t>piotrpietrzak@interia.pl</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>maria_wojcicka@domena..pl</t>
+          <t>maria_wojcicka@o2.pl</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>michal.czarnecki82@onet.pl</t>
+          <t>michal.czarnecki82@proton.me</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>joanna.lis@interia.pl</t>
+          <t>joanna.lis@outlook.com</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>p.kolodziej@o2.pl</t>
+          <t>p.kolodziej@yahoo.com</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>kaczmarek.magdalena@proton.me</t>
+          <t>kaczmarek.magdalena@icloud.com</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>robertpiatek@.pl</t>
+          <t>robertpiatek@gmail.com</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>agnieszka_sadowska@yahoo.com</t>
+          <t>agnieszka_sadowska@wp.pl</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>wojciech.wlodarczyk88@icloud.com</t>
+          <t>wojciech.wlodarczyk88@onet.pl</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>justyna.borkowska@gmail.com</t>
+          <t>justyna.borkowska@interia.pl</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>p.kowalski@wp.pl</t>
+          <t>p.kowalski@o2.pl</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>nowacka.maria@domena..pl</t>
+          <t>nowacka.maria@proton.me</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>michalwisniewski@interia.pl</t>
+          <t>michalwisniewski@outlook.com</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>joanna_wojcik@o2.pl</t>
+          <t>joanna_wojcik@yahoo.com</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>pawel.kowalczyk94@proton.me</t>
+          <t>pawel.kowalczyk94@icloud.com</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>magdalena.kaminska@outlook.com</t>
+          <t>magdalena.kaminska@gmail.com</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>r.lewandowski@yahoo.com</t>
+          <t>r.lewandowski@wp.pl</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>zielinska.agnieszka@wp</t>
+          <t>zielinska.agnieszka@onet.pl</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -14281,7 +14281,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>wojciechszymanski@gmail.com</t>
+          <t>wojciechszymanski@interia.pl</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>justyna_dabrowska@wp.pl</t>
+          <t>justyna_dabrowska@o2.pl</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>piotr.mazur71@onet.pl</t>
+          <t>piotr.mazur71@proton.me</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>maria.krawczyk@interia.pl</t>
+          <t>maria.krawczyk@outlook.com</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>@m.wozniak.invalid</t>
+          <t>email.20740157@yahoo.com</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>jankowska.joanna@proton.me</t>
+          <t>jankowska.joanna@icloud.com</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>pawelgrabowski@outlook.com</t>
+          <t>pawelgrabowski@gmail.com</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>magdalena_pawlak@yahoo.com</t>
+          <t>magdalena_pawlak@wp.pl</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>robert.michalski77@icloud.com</t>
+          <t>robert.michalski77@onet.pl</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>agnieszka.krol@wp</t>
+          <t>agnieszka.krol@interia.pl</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>w.wieczorek@wp.pl</t>
+          <t>w.wieczorek@o2.pl</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>jablonska.justyna@onet.pl</t>
+          <t>jablonska.justyna@proton.me</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>piotrwitkowski@interia.pl</t>
+          <t>piotrwitkowski@outlook.com</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>maria_walczak@o2.pl</t>
+          <t>maria_walczak@yahoo.com</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>@michal.stepien83.invalid</t>
+          <t>email.20740167@icloud.com</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>joanna.baran@outlook.com</t>
+          <t>joanna.baran@gmail.com</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>p.rutkowski@yahoo.com</t>
+          <t>p.rutkowski@wp.pl</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>gorska.magdalena@icloud.com</t>
+          <t>gorska.magdalena@onet.pl</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>robertsikora@gmail.com</t>
+          <t>robertsikora@interia.pl</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>agnieszka_ostrowska@wp</t>
+          <t>agnieszka_ostrowska@o2.pl</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>wojciech.tomaszewski89@onet.pl</t>
+          <t>wojciech.tomaszewski89@proton.me</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>justyna.zajac@interia.pl</t>
+          <t>justyna.zajac@outlook.com</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -16305,7 +16305,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>p.pietrzak@o2.pl</t>
+          <t>p.pietrzak@yahoo.com</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>wojcicka.maria@proton.me</t>
+          <t>wojcicka.maria@icloud.com</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>@michalczarnecki.invalid</t>
+          <t>email.20740177@gmail.com</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>joanna_lis@yahoo.com</t>
+          <t>joanna_lis@wp.pl</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>pawel.kolodziej95@icloud.com</t>
+          <t>pawel.kolodziej95@onet.pl</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>magdalena.kaczmarek@gmail.com</t>
+          <t>magdalena.kaczmarek@interia.pl</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>r.piatek@wp.pl</t>
+          <t>r.piatek@o2.pl</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>sadowska.agnieszka@wp</t>
+          <t>sadowska.agnieszka@proton.me</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>wojciechwlodarczyk@interia.pl</t>
+          <t>wojciechwlodarczyk@outlook.com</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>justyna_borkowska@o2.pl</t>
+          <t>justyna_borkowska@yahoo.com</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>piotr.kowalski72@proton.me</t>
+          <t>piotr.kowalski72@icloud.com</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>maria.nowacka@outlook.com</t>
+          <t>maria.nowacka@gmail.com</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -17409,7 +17409,7 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>@m.wisniewski.invalid</t>
+          <t>email.20740187@wp.pl</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>wojcik.joanna@icloud.com</t>
+          <t>wojcik.joanna@onet.pl</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>pawelkowalczyk@gmail.com</t>
+          <t>pawelkowalczyk@interia.pl</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>magdalena_kaminska@wp.pl</t>
+          <t>magdalena_kaminska@o2.pl</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>robert.lewandowski78@onet.pl</t>
+          <t>robert.lewandowski78@proton.me</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
@@ -17869,7 +17869,7 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>agnieszka.zielinska@wp</t>
+          <t>agnieszka.zielinska@outlook.com</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>w.szymanski@o2.pl</t>
+          <t>w.szymanski@yahoo.com</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>dabrowska.justyna@proton.me</t>
+          <t>dabrowska.justyna@icloud.com</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
@@ -18145,7 +18145,7 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>piotrmazur@outlook.com</t>
+          <t>piotrmazur@gmail.com</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>maria_krawczyk@yahoo.com</t>
+          <t>maria_krawczyk@wp.pl</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>@michal.wozniak84.invalid</t>
+          <t>email.20740197@onet.pl</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -18421,7 +18421,7 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>joanna.jankowska@gmail.com</t>
+          <t>joanna.jankowska@interia.pl</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>p.grabowski@wp.pl</t>
+          <t>p.grabowski@o2.pl</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">

--- a/data/xlsx/ceidg.xlsx
+++ b/data/xlsx/ceidg.xlsx
@@ -140,7 +140,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -150,7 +150,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -205,7 +205,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>magdalena.pawlak.sikora@gmail.com</t>
+          <t>anna.kowalska.krawczyk@gmail.com</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -232,17 +232,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>r.michalski@outlook.com</t>
+          <t>t.nowacki@outlook.com</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -324,17 +324,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>krol.agnieszka@wp.pl</t>
+          <t>wisniewska.katarzyna@wp.pl</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -416,7 +416,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -426,7 +426,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>wojciechwieczorek@onet.pl</t>
+          <t>krzysztofwojcik@onet.pl</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>justyna_jablonska@interia.pl</t>
+          <t>ewa_kowalczyk@interia.pl</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -600,17 +600,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>piotr.witkowski75@o2.pl</t>
+          <t>adam.kaminski75@o2.pl</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Lewandowska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>maria.walczak@proton.me</t>
+          <t>monika.lewandowska@proton.me</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FIRMAID-00608</t>
+          <t>IFRMAID-00608</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Marke</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>m.stepien@yahoo.com</t>
+          <t>m.zielinski@yahoo.com</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -876,17 +876,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Joanna</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Barbara</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>baran.joanna@gmail.com</t>
+          <t>szymanska.barbara@gmail.com</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>79112119190</t>
+          <t>69112119190</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>pawelrutkowski@outlook.com</t>
+          <t>rafaldabrowski@outlook.com</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Magdalena</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>magdalena_gorska@wp.pl</t>
+          <t>anna_mazur@wp.pl</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>robert.sikora81@onet.pl</t>
+          <t>tomasz.krawczyk81@onet.pl</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>agnieszka.ostrowska@interia.pl</t>
+          <t>katarzyna.wozniak@interia.pl</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Wojciech</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>w.tomaszewski@o2.pl</t>
+          <t>k.jankowski@o2.pl</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1428,17 +1428,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>zajac.justyna@proton.me</t>
+          <t>grabowska.ewa@proton.me</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>piotrpietrzak@yahoo.com</t>
+          <t>adampawlak@yahoo.com</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1612,17 +1612,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>maria_wojcicka@gmail.com</t>
+          <t>monika_michalska@gmail.com</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Marek</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>michal.czarnecki87@outlook.com</t>
+          <t>marek.krol87@outlook.com</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1236230886</t>
+          <t>2236230886</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>joanna.lis@wp.pl</t>
+          <t>barbara.wieczorek@wp.pl</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1888,17 +1888,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Paweł</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Rafał</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>p.kolodziej@onet.pl</t>
+          <t>r.jablonski@onet.pl</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>Magdalena</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>kaczmarek.magdalena@interia.pl</t>
+          <t>witkowska.anna@interia.pl</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2236468458</t>
+          <t>1236468458</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>robertpiatek@o2.pl</t>
+          <t>tomaszwalczak@o2.pl</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2164,17 +2164,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>agnieszka_sadowska@proton.me</t>
+          <t>katarzyna_stepien@proton.me</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Wojciech</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>wojciech.wlodarczyk93@yahoo.com</t>
+          <t>krzysztof.baran93@yahoo.com</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>justyna.borkowska@gmail.com</t>
+          <t>ewa.rutkowska@gmail.com</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>p.kowalski@outlook.com</t>
+          <t>a.gorski@outlook.com</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2532,17 +2532,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>nowacka.maria@wp.pl</t>
+          <t>sikora.monika@wp.pl</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>michalwisniewski@onet.pl</t>
+          <t>marekostrowski@onet.pl</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Joanna</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Barbara</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>joanna_wojcik@interia.pl</t>
+          <t>barbara_tomaszewska@interia.pl</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2808,17 +2808,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Paweł</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Rafał</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>337260358</t>
+          <t>237260358</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>pawel.kowalczyk70@o2.pl</t>
+          <t>rafal.zajac70@o2.pl</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>magdalena.kaminska@proton.me</t>
+          <t>anna.pietrzak@proton.me</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>r.lewandowski@yahoocom</t>
+          <t>t.wojcicki@yahoocom</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3084,17 +3084,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>zielinska.agnieszka@gmail.com</t>
+          <t>czarnecka.katarzyna@gmail.com</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>wojciechszymanski@outlook.com</t>
+          <t>krzysztoflis@outlook.com</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3268,17 +3268,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>justyna_dabrowska@wp.pl</t>
+          <t>ewa_kolodziej@wp.pl</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3360,17 +3360,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>piotr.mazur76@onet.pl</t>
+          <t>adam.kaczmarek76@onet.pl</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>237893879</t>
+          <t>337893879</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>maria.krawczyk@interia.pl</t>
+          <t>monika.piatek@interia.pl</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Marek</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>m.wozniak@o2.pl</t>
+          <t>m.sadowski@o2.pl</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>Joanna</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Barbara</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>jankowska.joanna@proton.me</t>
+          <t>wlodarczyk.barbara@proton.me</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>pawelgrabowski@yahoo.com</t>
+          <t>rafalborkowski@yahoo.com</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3820,17 +3820,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>Magdalena</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>magdalena_pawlak.sikora@gmail.com</t>
+          <t>anna_kowalska.krawczyk@gmail.com</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3912,17 +3912,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>robert.michalski82@outlook.com</t>
+          <t>tomasz.nowacki82@outlook.com</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>agnieszka.krol@wp.pl</t>
+          <t>katarzyna.wisniewska@wp.pl</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4096,17 +4096,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>Wojciech</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>w.wieczorek@onet.pl</t>
+          <t>k.wojcik@onet.pl</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4188,17 +4188,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>jablonska.justyna@interia.pl</t>
+          <t>kowalczyk.ewa@interia.pl</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>piotrwitkowski@o2.pl</t>
+          <t>adamkaminski@o2.pl</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4372,17 +4372,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Lewandowska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>maria_walczak@proton.me</t>
+          <t>monika_lewandowska@proton.me</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4464,17 +4464,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Marek</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>michal.stepien88@yahoo.com</t>
+          <t>marek.zielinski88@yahoo.com</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>joanna.baran@gmail.com</t>
+          <t>barbara.szymanska@gmail.com</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4648,17 +4648,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>Paweł</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Rafał</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>p.rutkowski@finanse24.xs</t>
+          <t>r.dabrowski@finanse24.xs</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4740,17 +4740,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>Magdalena</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>gorska.magdalena@wp.pl</t>
+          <t>mazur.anna@wp.pl</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>robertsikora@onet.pl</t>
+          <t>tomaszkrawczyk@onet.pl</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4924,17 +4924,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>agnieszka_ostrowska@interia.pl</t>
+          <t>katarzyna_wozniak@interia.pl</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5016,17 +5016,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>Wojciech</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>wojciech.tomaszewski94@o2.pl</t>
+          <t>krzysztof.jankowski94@o2.pl</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>justyna.zajac@proton.me</t>
+          <t>ewa.grabowska@proton.me</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5200,17 +5200,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>p.pietrzak@yahoo.com</t>
+          <t>a.pawlak@yahoo.com</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5292,17 +5292,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>wojcicka.maria@gmail.com</t>
+          <t>michalska.monika@gmail.com</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Quantum Services</t>
+          <t>Quantum Sevrices</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>michalczarnecki@outlook.com</t>
+          <t>marekkrol@outlook.com</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5476,17 +5476,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>Joanna</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Barbara</t>
-        </is>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>joanna_lis@wp.pl</t>
+          <t>barbara_wieczorek@wp.pl</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5568,22 +5568,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>Paweł</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Rafał</t>
-        </is>
-      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>83010787692</t>
+          <t>73010787692</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>pawel.kolodziej71@onet.pl</t>
+          <t>rafal.jablonski71@onet.pl</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>magdalena.kaczmarek@interia.pl</t>
+          <t>anna.witkowska@interia.pl</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5752,17 +5752,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>r.piatek@o2.pl</t>
+          <t>t.walczak@o2.pl</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5844,17 +5844,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>sadowska.agnieszka@proton.me</t>
+          <t>stepien.katarzyna@proton.me</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>wojciechwlodarczyk@yahoo.com</t>
+          <t>krzysztofbaran@yahoo.com</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6028,17 +6028,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>justyna_borkowska@gmail.com</t>
+          <t>ewa_rutkowska@gmail.com</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6120,17 +6120,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>piotr.kowalski77@outlook.com</t>
+          <t>adam.gorski77@outlook.com</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>maria.nowacka@wp.pl</t>
+          <t>monika.sikora@wp.pl</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6304,17 +6304,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Marek</t>
-        </is>
-      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1240111194</t>
+          <t>2240111194</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>m.wisniewski@onet.pl</t>
+          <t>m.ostrowski@onet.pl</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6396,17 +6396,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>Joanna</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Barbara</t>
-        </is>
-      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>wojcik.joanna@interia.pl</t>
+          <t>tomaszewska.barbara@interia.pl</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>pawelkowalczyk@o2.pl</t>
+          <t>rafalzajac@o2.pl</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6580,17 +6580,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>Magdalena</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>magdalena_kaminska@proton.me</t>
+          <t>anna_pietrzak@proton.me</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6672,17 +6672,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2240427951</t>
+          <t>1240427951</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>robert.lewandowski83@yahoo.com</t>
+          <t>tomasz.wojcicki83@yahoo.com</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>agnieszka.zielinska@gmail.com</t>
+          <t>katarzyna.czarnecka@gmail.com</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>Wojciech</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>w.szymanski@outlook.com</t>
+          <t>k.lis@outlook.com</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6948,17 +6948,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>dabrowska.justyna@wp.pl</t>
+          <t>kolodziej.ewa@wp.pl</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>piotrmazur@onet.pl</t>
+          <t>adamkaczmarek@onet.pl</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7132,17 +7132,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>maria_krawczyk@interia.pl</t>
+          <t>monika_piatek@interia.pl</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7224,17 +7224,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Marek</t>
-        </is>
-      </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>michal.wozniak89@o2.pl</t>
+          <t>marek.sadowski89@o2.pl</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>341140668</t>
+          <t>241140668</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>joanna.jankowska@proton.me</t>
+          <t>barbara.wlodarczyk@proton.me</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7408,17 +7408,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Paweł</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Rafał</t>
-        </is>
-      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>p.grabowski@yahoo.com</t>
+          <t>r.borkowski@yahoo.com</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7500,17 +7500,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Magdalena</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>pawlak.sikora.magdalena@gmail.com</t>
+          <t>kowalska.krawczyk.anna@gmail.com</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>robertmichalski@outlook.com</t>
+          <t>tomasznowacki@outlook.com</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t/>
+          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7684,17 +7684,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>787918944</t>
+          <t/>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>agnieszka_krol@wp.pl</t>
+          <t>katarzyna_wisniewska@wp.pl</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7776,17 +7776,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Wojciech</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>wojciech.wieczorek95@onet.pl</t>
+          <t>krzysztof.wojcik95@onet.pl</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>justyna.jablonska@interia.pl</t>
+          <t>ewa.kowalczyk@interia.pl</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7960,17 +7960,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>241694993</t>
+          <t>341694993</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>p.witkowski@o2.pl</t>
+          <t>a.kaminski@o2.pl</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -8052,17 +8052,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Lewandowska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1241615809</t>
+          <t/>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>walczak.maria@proton.me</t>
+          <t>lewandowska.monika@proton.me</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>michalstepien@yahoo.com</t>
+          <t>marekzielinski@yahoo.com</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8236,17 +8236,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>Joanna</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Barbara</t>
-        </is>
-      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t/>
+          <t>1241774181</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>joanna_baran@gmail.com</t>
+          <t>barbara_szymanska@gmail.com</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8328,17 +8328,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>Paweł</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Rafał</t>
-        </is>
-      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>pawel.rutkowski72@outlook.com</t>
+          <t>rafal.dabrowski72@outlook.com</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>magdalena.gorska@wp.pl</t>
+          <t>anna.mazur@wp.pl</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8512,17 +8512,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>r.sikora@onet.pl</t>
+          <t>t.krawczyk@onet.pl</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8604,17 +8604,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>ostrowska.agnieszka@interia.pl</t>
+          <t>wozniak.katarzyna@interia.pl</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>wojciechtomaszewski@o2.pl</t>
+          <t>krzysztofjankowski@o2.pl</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8788,17 +8788,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>justyna_zajac@proton.me</t>
+          <t>ewa_grabowska@proton.me</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8880,17 +8880,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>piotr.pietrzak78@yahoo.com</t>
+          <t>adam.pawlak78@yahoo.com</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>maria.wojcicka@gmail.com</t>
+          <t>monika.michalska@gmail.com</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -9064,17 +9064,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Marek</t>
-        </is>
-      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>m.czarnecki@outlook.com</t>
+          <t>m.krol@outlook.com</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -9156,17 +9156,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>Joanna</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Barbara</t>
-        </is>
-      </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>lis.joanna@wp.pl</t>
+          <t>wieczorek.barbara@wp.pl</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>pawelkolodziej@ubezpiecznia.pl</t>
+          <t>rafaljablonski@ubezpiecznia.pl</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>Magdalena</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>magdalena_kaczmarek@interia.pl</t>
+          <t>anna_witkowska@interia.pl</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9432,17 +9432,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>robert.piatek84@o2.pl</t>
+          <t>tomasz.walczak84@o2.pl</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>agnieszka.sadowska@proton.me</t>
+          <t>katarzyna.stepien@proton.me</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9616,17 +9616,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>Wojciech</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>w.wlodarczyk@yahoo.com</t>
+          <t>k.baran@yahoo.com</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9708,17 +9708,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>borkowska.justyna@gmail.com</t>
+          <t>rutkowska.ewa@gmail.com</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>piotrkowalski@outlook.com</t>
+          <t>adamgorski@outlook.com</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9892,17 +9892,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>maria_nowacka@wp.pl</t>
+          <t>monika_sikora@wp.pl</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9979,22 +9979,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Qauntum Services</t>
+          <t>Quantum Services</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Marek</t>
-        </is>
-      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>michal.wisniewski90@onet.pl</t>
+          <t>marek.ostrowski90@onet.pl</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>joanna.wojcik@interia.pl</t>
+          <t>barbara.tomaszewska@interia.pl</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -10168,22 +10168,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>Paweł</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Rafał</t>
-        </is>
-      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>87032156193</t>
+          <t>77032156193</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>p.kowalczyk@o2.pl</t>
+          <t>r.zajac@o2.pl</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -10260,17 +10260,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
           <t>Magdalena</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>kaminska.magdalena@proton.me</t>
+          <t>pietrzak.anna@proton.me</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>robertlewandowski@yahoo.com</t>
+          <t>tomaszwojcicki@yahoo.com</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10444,17 +10444,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>agnieszka_zielinska@gmail.com</t>
+          <t>katarzyna_czarnecka@gmail.com</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10536,17 +10536,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>Wojciech</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>wojciech.szymanski96@outlook.com</t>
+          <t>krzysztof.lis96@outlook.com</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>justyna.dabrowska@wp.pl</t>
+          <t>ewa.kolodziej@wp.pl</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10720,22 +10720,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>83090764416</t>
+          <t>93090764416</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>p.mazur@onet.pl</t>
+          <t>a.kaczmarek@onet.pl</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10812,17 +10812,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1243991505</t>
+          <t>2243991505</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>krawczyk.maria@interia.pl</t>
+          <t>piatek.monika@interia.pl</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>michalwozniak@o2.pl</t>
+          <t>mareksadowski@o2.pl</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10996,17 +10996,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
           <t>Joanna</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Barbara</t>
-        </is>
-      </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>joanna_jankowska@proton.me</t>
+          <t>barbara_wlodarczyk@proton.me</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -11088,17 +11088,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
           <t>Paweł</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Rafał</t>
-        </is>
-      </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>pawel.grabowski73@yahoo.com</t>
+          <t>rafal.borkowski73@yahoo.com</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>magdalena.pawlak.sikora@gmail.com</t>
+          <t>anna.kowalska.krawczyk@gmail.com</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -11272,17 +11272,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2244387450</t>
+          <t>1244387450</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>r.michalski@outlook.com</t>
+          <t>t.nowacki@outlook.com</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -11364,17 +11364,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>krol.agnieszka@wp.pl</t>
+          <t>wisniewska.katarzyna@wp.pl</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>wojciechwieczorek@onet.pl</t>
+          <t>krzysztofwojcik@onet.pl</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11548,17 +11548,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>justyna_jablonska@interia.pl</t>
+          <t>ewa_kowalczyk@interia.pl</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11640,17 +11640,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>piotr.witkowski79@o2.pl</t>
+          <t>adam.kaminski79@o2.pl</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Lewandowska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>maria.walczak@proton.me</t>
+          <t>monika.lewandowska@proton.me</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11824,17 +11824,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Marek</t>
-        </is>
-      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>345020978</t>
+          <t>245020978</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>m.stepien@yahoo.com</t>
+          <t>m.zielinski@yahoo.com</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11916,17 +11916,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>Joanna</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Barbara</t>
-        </is>
-      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>baran.joanna@gmail.com</t>
+          <t>szymanska.barbara@gmail.com</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>pawelrutkowski@outlook.com</t>
+          <t>rafaldabrowski@outlook.com</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -12100,17 +12100,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>Magdalena</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>magdalena_gorska@wp.pl</t>
+          <t>anna_mazur@wp.pl</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -12192,17 +12192,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>robert.sikora85onet.pl</t>
+          <t>tomasz.krawczyk85onet.pl</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>agnieszka.ostrowska@interia.pl</t>
+          <t>katarzyna.wozniak@interia.pl</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -12376,17 +12376,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
           <t>Wojciech</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>w.tomaszewski@o2.pl</t>
+          <t>k.jankowski@o2.pl</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12468,17 +12468,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>245575305</t>
+          <t>345575305</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>zajac.justyna@proton.me</t>
+          <t>grabowska.ewa@proton.me</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>piotrpietrzak@yahoo.com</t>
+          <t>adampawlak@yahoo.com</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12652,17 +12652,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>maria_wojcicka@gmail.com</t>
+          <t>monika_michalska@gmail.com</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12744,17 +12744,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Marek</t>
-        </is>
-      </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>michal.czarnecki91@outlook.com</t>
+          <t>marek.krol91@outlook.com</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>joanna.lis@wp.pl</t>
+          <t>barbara.wieczorek@wp.pl</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12928,17 +12928,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
           <t>Paweł</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Rafał</t>
-        </is>
-      </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>p.kolodziej@onet.pl</t>
+          <t>r.jablonski@onet.pl</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -13020,17 +13020,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
           <t>Magdalena</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>kaczmarek.magdalena@interia.pl</t>
+          <t>witkowska.anna@interia.pl</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>robertpiatek@o2.pl</t>
+          <t>tomaszwalczak@o2.pl</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>agnieszka_sadowska@proton.me</t>
+          <t>katarzyna_stepien@proton.me</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -13296,17 +13296,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
           <t>Wojciech</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>wojciech.wlodarczyk97@yahoo.com</t>
+          <t>krzysztof.baran97@yahoo.com</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>justyna.borkowska@gmail.com</t>
+          <t>ewa.rutkowska@gmail.com</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -13480,17 +13480,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>p.kowalski@outlook.com</t>
+          <t>a.gorski@outlook.com</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13572,17 +13572,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>nowacka.maria@wp.pl</t>
+          <t>sikora.monika@wp.pl</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>michalwisniewski@onet.pl</t>
+          <t>marekostrowski@onet.pl</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13756,17 +13756,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
           <t>Joanna</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Barbara</t>
-        </is>
-      </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>joanna_wojcik@interia.pl</t>
+          <t>barbara_tomaszewska@interia.pl</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13848,17 +13848,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
           <t>Paweł</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Rafał</t>
-        </is>
-      </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>pawel.kowalczyk74@abxza.pl</t>
+          <t>rafal.zajac74@abxza.pl</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13950,7 +13950,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>magdalena.kaminska@proton.me</t>
+          <t>anna.pietrzak@proton.me</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -14032,17 +14032,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>r.lewandowski@yahoo.com</t>
+          <t>t.wojcicki@yahoo.com</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -14124,17 +14124,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>zielinska.agnieszka@gmail.com</t>
+          <t>czarnecka.katarzyna@gmail.com</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -14281,7 +14281,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>wojciechszymanski@outlook.com</t>
+          <t>krzysztoflis@outlook.com</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -14308,17 +14308,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>justyna_dabrowska@wp.pl</t>
+          <t>ewa_kolodziej@wp.pl</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -14400,17 +14400,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>piotr.mazur80@onet.pl</t>
+          <t>adam.kaczmarek80@onet.pl</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>maria.krawczyk@interia.pl</t>
+          <t>monika.piatek@interia.pl</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -14579,22 +14579,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Quantu Services</t>
+          <t>Qauntum Services</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Marek</t>
-        </is>
-      </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>m.wozniak@o2.pl</t>
+          <t>m.sadowski@o2.pl</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14676,17 +14676,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
           <t>Joanna</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Barbara</t>
-        </is>
-      </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>jankowska.joanna@proton.me</t>
+          <t>wlodarczyk.barbara@proton.me</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14778,12 +14778,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>91050724690</t>
+          <t>81050724690</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>pawelgrabowski@yahoo.com</t>
+          <t>rafalborkowski@yahoo.com</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14860,17 +14860,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
           <t>Magdalena</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>magdalena_pawlak.sikora@gmail.com</t>
+          <t>anna_kowalska.krawczyk@gmail.com</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>robert.michalski86@outlook.com</t>
+          <t>tomasz.nowacki86@outlook.com</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>agnieszka.krol@wp.pl</t>
+          <t>katarzyna.wisniewska@wp.pl</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -15136,17 +15136,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
           <t>Wojciech</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>w.wieczorek@onet.pl</t>
+          <t>k.wojcik@onet.pl</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -15228,17 +15228,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>jablonska.justyna@interia.pl</t>
+          <t>kowalczyk.ewa@interia.pl</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -15340,7 +15340,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>1247871815</t>
+          <t>2247871815</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>piotrwitkowski@o2.pl</t>
+          <t>adamkaminski@o2.pl</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -15412,17 +15412,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Lewandowska</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>maria_walczak@proton.me</t>
+          <t>monika_lewandowska@proton.me</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -15504,17 +15504,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Marek</t>
-        </is>
-      </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>michal.stepien92@yahoo.com</t>
+          <t>marek.zielinski92@yahoo.com</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>joanna.baran@gmail.com</t>
+          <t>barbara.szymanska@gmail.com</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
           <t>Paweł</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Rafał</t>
-        </is>
-      </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>p.rutkowski@outlook.com</t>
+          <t>r.dabrowski@outlook.com</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15780,17 +15780,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
           <t>Magdalena</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>gorska.magdalena@wp.pl</t>
+          <t>mazur.anna@wp.pl</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15882,7 +15882,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2248346956</t>
+          <t>1248346956</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>robertsikora@onet.pl</t>
+          <t>tomaszkrawczyk@onet.pl</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -15964,17 +15964,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>agnieszka_ostrowska@interia.pl</t>
+          <t>katarzyna_wozniak@interia.pl</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -16056,17 +16056,17 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
           <t>Wojciech</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>wojciech.tomaszewski98@o2.pl</t>
+          <t>krzysztof.jankowski98@o2.pl</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>justyna.zajac@proton.me</t>
+          <t>ewa.grabowska@proton.me</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -16240,17 +16240,17 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -16305,7 +16305,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>p.pietrzak@yahoo.com</t>
+          <t>a.pawlak@yahoo.com</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -16332,17 +16332,17 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>348901283</t>
+          <t>248901283</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>wojcicka.maria@gmail.com</t>
+          <t>michalska.monika@gmail.com</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -16434,7 +16434,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>michalczarnecki@outlook.com</t>
+          <t>marekkrol@outlook.com</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -16516,17 +16516,17 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
           <t>Joanna</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Barbara</t>
-        </is>
-      </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>joanna_lis@wp.pl</t>
+          <t>barbara_wieczorek@wp.pl</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -16608,17 +16608,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
           <t>Paweł</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Rafał</t>
-        </is>
-      </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>pawel.kolodziej75@onet.pl</t>
+          <t>rafal.jablonski75@onet.pl</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>magdalena.kaczmarek@interia.pl</t>
+          <t>anna.witkowska@interia.pl</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -16792,17 +16792,17 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>r.piatek@o2.pl</t>
+          <t>t.walczak@o2.pl</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -16884,17 +16884,17 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>sadowska.agnieszka@proton.me</t>
+          <t>stepien.katarzyna@proton.me</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -17001,7 +17001,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>249455615</t>
+          <t>349455615</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>wojciechwlodarczyk@yahoo.com</t>
+          <t>krzysztofbaran@yahoo.com</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -17068,17 +17068,17 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>justyna_borkowska@gmail.com</t>
+          <t>ewa_rutkowska@gmail.com</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>piotr.kowalski81@outlook.com</t>
+          <t>adam.gorski81@outlook.com</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>maria.nowacka@wp.pl</t>
+          <t>monika.sikora@wp.pl</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -17344,17 +17344,17 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Marek</t>
-        </is>
-      </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -17409,7 +17409,7 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>m.wisniewski@onet.pl</t>
+          <t>m.ostrowski@onet.pl</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -17436,17 +17436,17 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
           <t>Joanna</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Barbara</t>
-        </is>
-      </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>wojcik.joanna@interia.pl</t>
+          <t>tomaszewska.barbara@interia.pl</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>pawelkowalczyk@o2.pl</t>
+          <t>rafalzajac@o2.pl</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
@@ -17620,17 +17620,17 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
           <t>Magdalena</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>magdalena_kaminska@proton.me</t>
+          <t>anna_pietrzak@proton.me</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
@@ -17712,17 +17712,17 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
           <t>Robert</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>robert.lewandowski87@yahoo.com</t>
+          <t>tomasz.wojcicki87@yahoo.com</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -17869,7 +17869,7 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>agnieszka.zielinska@gmail.com</t>
+          <t>katarzyna.czarnecka@gmail.com</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -17896,17 +17896,17 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
           <t>Wojciech</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>w.szymanski@outlook.com</t>
+          <t>k.lis@outlook.com</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -17988,17 +17988,17 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
           <t>Justyna</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>dabrowska.justyna@wp.pl</t>
+          <t>kolodziej.ewa@wp.pl</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
@@ -18080,7 +18080,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -18090,7 +18090,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -18145,7 +18145,7 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>piotrmazur@onet.pl</t>
+          <t>adamkaczmarek@onet.pl</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -18172,17 +18172,17 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>maria_krawczyk@interia.pl</t>
+          <t>monika_piatek@interia.pl</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -18264,17 +18264,17 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
+          <t>Marek</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
           <t>Michał</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Marek</t>
-        </is>
-      </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>michal.wozniak93@o2.pl</t>
+          <t>marek.sadowski93@o2.pl</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -18356,7 +18356,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -18366,7 +18366,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -18421,7 +18421,7 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>joanna.jankowska@proton.me</t>
+          <t>barbara.wlodarczyk@proton.me</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -18448,17 +18448,17 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
           <t>Paweł</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Rafał</t>
-        </is>
-      </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>p.grabowski@uuu.xs</t>
+          <t>r.borkowski@uuu.xs</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">

--- a/data/xlsx/ceidg.xlsx
+++ b/data/xlsx/ceidg.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2021-08-06</t>
+          <t>2024/15/09</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2020-02-02</t>
+          <t>20270302</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2021-07-10</t>
+          <t>03/07/2024</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>07/12/2023</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2025/23/10</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2022-02-03</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2021-09-05</t>
+          <t>31-05-2025</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
+          <t>11/06/2023</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2023-03-10</t>
+          <t>11-05-2024</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2022-02-02</t>
+          <t>01/12/2022</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>20220109</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>20260220</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>20261102</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>13/01/2025</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>20251023</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
+          <t>02/11/2026</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2025/07/01</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2027-02-03</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2020-02-07</t>
+          <t>2022/30/10</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -15820,7 +15820,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>05-10-2024</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026/20/02</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
+          <t>2026/02/11</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">

--- a/data/xlsx/ceidg.xlsx
+++ b/data/xlsx/ceidg.xlsx
@@ -150,12 +150,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kowalska-Krawczyk</t>
+          <t>Lewandowska-Król</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>60021406849</t>
+          <t>62021428841</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -205,7 +205,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>anna.kowalska.krawczyk@gmail.com</t>
+          <t>anna.lewandowska.krol@gmail.com</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -222,12 +222,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zielony Bieszczady S.A.</t>
+          <t>Pewny Delfin S.A.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Zielony Bieszczady</t>
+          <t>Pewny Delfin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -242,12 +242,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>61032108236</t>
+          <t>63032130231</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -297,12 +297,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>t.nowacki@outlook.com</t>
+          <t>t.zielinski@outlook.com</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://zielony-bieszczady.eu</t>
+          <t>https://pewny-delfin.eu</t>
         </is>
       </c>
     </row>
@@ -314,12 +314,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zielony Karpaty SA</t>
+          <t>Dobry Koral SA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Zielony Karpaty</t>
+          <t>Dobry Koral</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -334,12 +334,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>62042809586</t>
+          <t>64042831581</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -389,12 +389,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>wisniewska.katarzyna@wp.pl</t>
+          <t>szymanska.katarzyna@wp.pl</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://www.zielony-karpaty-group.local</t>
+          <t>https://www.dobry-koral-group.local</t>
         </is>
       </c>
     </row>
@@ -406,12 +406,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zielony Bałtyk S. A.</t>
+          <t>Polski Szafir S. A.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Zielony Bałtyk</t>
+          <t>Polski Szafir</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>63050710972</t>
+          <t>65050732974</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -481,12 +481,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>krzysztofwojcik@onet.pl</t>
+          <t>krzysztofdabrowski@onet.pl</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://www.zielony-baltyk-group.pl</t>
+          <t>https://www.polski-szafir-group.pl</t>
         </is>
       </c>
     </row>
@@ -498,12 +498,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zielony Sudety Spółka Akcyjna</t>
+          <t>Europejski Orzeł Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zielony Sudety</t>
+          <t>Europejski Orzeł</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -518,12 +518,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>64061412321</t>
+          <t>66061434323</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ewa_kowalczyk@interia.pl</t>
+          <t>ewa_mazur@interia.pl</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>https://www.zielony-sudety-group.com.pl</t>
+          <t>https://www.europejski-orzel-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Niebieski Amber sp. z o.o.</t>
+          <t>Globalny Kaktus sp. z o.o.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Niebieski Amber</t>
+          <t>Globalny Kaktus</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>65072113717</t>
+          <t>67072135719</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>adam.kaminski95@o2.pl</t>
+          <t>adam.krawczyk95@o2.pl</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://www.niebieski-amber.eu</t>
+          <t>https://www.globalny-kaktus.eu</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Niebieski Bizon sp z oo</t>
+          <t>Lokalny Olimp sp z oo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Niebieski Bizon</t>
+          <t>Lokalny Olimp</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>66082815068</t>
+          <t>68082837060</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>monika.lewandowska@proton.me</t>
+          <t>monika.wozniak@proton.me</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Niebieski Canyon sp. z o. o.</t>
+          <t>Nowoczesny Beskid sp. z o. o.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Niebieski Canyon</t>
+          <t>Nowocezsny Beskid</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>67090716451</t>
+          <t>69090738453</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>m.zielinski@yahoo.com</t>
+          <t>m.jankowski@yahoo.com</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://www.niebieski-canyon-group.pl</t>
+          <t>https://www.nowoczesny-beskid-group.pl</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Niebieski Delfin Sp. z o.o.</t>
+          <t>Tradycyjny Canyon Sp. z o.o.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Niebieski Delfin</t>
+          <t>Tradycyjny Canyon</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>68101417802</t>
+          <t>70101439803</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>szymanska.barbara@gmail.com</t>
+          <t>grabowska.barbara@gmail.com</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://www.niebieski-delfin-group.com.pl</t>
+          <t>https://www.tradycyjny-canyon-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Niebieski Echo SP Z O O</t>
+          <t>Dynamiczny Jantar SP Z O O</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Niebieski Echo</t>
+          <t>Dynamiczny Jantar</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>69112119190</t>
+          <t>71112141194</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>rafaldabrowski@outlook.com</t>
+          <t>rafalpawlak@outlook.com</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://www.niebieski-echo-group.eu</t>
+          <t>https://www.dynamiczny-jantar-group.eu</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Niebieski Falcon spółka z ograniczoną odpowiedzialnością</t>
+          <t>Stabilny Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Niebieski Falcon</t>
+          <t>Stabilny Rubin</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>70122820541</t>
+          <t>72122842543</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>aleksandra_mazur@wp.pl</t>
+          <t>aleksandra_michalska@wp.pl</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://www.niebieski-falcon.local</t>
+          <t>https://www.stabilny-rubin.local</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Niebieski Gryf Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Innowacyjny Sokół Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Niebieski Gryf</t>
+          <t>Innowacyjny Sokół</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>71010721939</t>
+          <t>73010743931</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>andrzej.krawczyk72@onet.pl</t>
+          <t>andrzej.krol72@onet.pl</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://niebieski-gryf.pl</t>
+          <t>https://innowacyjny-sokol.pl</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Niebieski Horyzont S.A.</t>
+          <t>Kreatywny Jodełka S.A.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Niebieski Horyzont</t>
+          <t>Kreatywny Jodełka</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>72021423289</t>
+          <t>74021445281</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>marta.wozniak@interia.pl</t>
+          <t>marta.wieczorek@interia.pl</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Niebieski Ikar SA</t>
+          <t>Aktywny Zodiak SA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Niebieski Ikar</t>
+          <t>Aktywny Zodiak</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>73032124675</t>
+          <t>75032146677</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>l.jankowski@o2.pl</t>
+          <t>l.jablonski@o2.pl</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>https://www.niebieski-ikar-group.eu</t>
+          <t>https://www.aktywny-zodiak-group.eu</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Niebieski Jantar S. A.</t>
+          <t>Jasny Kasprowy S. A.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Niebieski Jantar</t>
+          <t>Jasny Kasprowy</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>74042826025</t>
+          <t>76042848027</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>grabowska.paulina@proton.me</t>
+          <t>witkowska.paulina@proton.me</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>https://www.niebieski-jantar-group.local</t>
+          <t>https://www.jasny-kasprowy-group.local</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Niebieski Koral Spółka Akcyjna</t>
+          <t>Green Bizon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Niebieski Koral</t>
+          <t>Green Bizon</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>75050727418</t>
+          <t>77050749410</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>mateuszpawlak@yahoo.com</t>
+          <t>mateuszwalczak@yahoo.com</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>https://www.niebieski-koral.pl</t>
+          <t>https://www.green-bizon.pl</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Niebieski Lotos sp. z o.o.</t>
+          <t>Blue Ikar sp. z o.o.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Niebieski Lotos</t>
+          <t>Blue Ikar</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>76061428767</t>
+          <t>78061450762</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>elzbieta_michalska@gmail.com</t>
+          <t>elzbieta_stepien@gmail.com</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>https://niebieski-lotos.com.pl</t>
+          <t>https://blue-ikar.com.pl</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Niebieski Magnolia sp z oo</t>
+          <t>Gold Pegaz sp z oo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Niebieski Magnolia</t>
+          <t>Gold Pegaz</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>77072130157</t>
+          <t>79072152159</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>dawid.krol78@outlook.com</t>
+          <t>dawid.baran78@outlook.com</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>https://www.niebieski-magnolia-group.eu</t>
+          <t>https://www.gold-pegaz-group.eu</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Niebieski Neon sp. z o. o.</t>
+          <t>Silver Żubr sp. z o. o.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Niebieski Neon</t>
+          <t>Silver Żubr</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>78082831506</t>
+          <t>80082853507</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>dorota.wieczorek@wp.pl</t>
+          <t>dorota.rutkowska@wp.pl</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Niebieski Oaza Sp. z o.o.</t>
+          <t>Smart Narew Sp. z o.o.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Niebieski Oaza</t>
+          <t>Smart Narew</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>79090732890</t>
+          <t>81090754891</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>d.jablonski@onet.pl</t>
+          <t>d.gorski@onet.pl</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>https://www.niebieski-oaza-group.pl</t>
+          <t>https://www.smart-narew-group.pl</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P.P.H.U. Niebieski Pegaz</t>
+          <t>P.P.H.U. Fast Syrena</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>P.P.H.U. Niebieski Pegaz</t>
+          <t>P.P.H.U. Fast Syrena</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>80101434241</t>
+          <t>82101456243</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>witkowska.beata@interia.pl</t>
+          <t>sikora.beata@interia.pl</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>https://www.niebieski-pegaz.com.pl</t>
+          <t>https://www.fast-syrena.com.pl</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Niebieski Rubin spółka z ograniczoną odpowiedzialnością</t>
+          <t>Safe Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Niebieski Rubin</t>
+          <t>Safe Rysy</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>81112135637</t>
+          <t>83112157639</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>slawomirwalczak@o2.pl</t>
+          <t>slawomirostrowski@o2.pl</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://niebieski-rubin.eu</t>
+          <t>https://safe-rysy.eu</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Niebieski Szafir Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Best Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Niebieski Szafir</t>
+          <t>Best Amber</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>82122836987</t>
+          <t>84122858989</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>urszula_stepien@proton.me</t>
+          <t>urszula_tomaszewska@proton.me</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://www.niebieski-szafir-group.local</t>
+          <t>https://www.best-amber-group.local</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Niebieski Tytan S.A.</t>
+          <t>Global Horyzont S.A.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Niebieski Tytan</t>
+          <t>Global Horyzont</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>83010738376</t>
+          <t>85010760371</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>mariusz.baran84@yahoo.com</t>
+          <t>mariusz.zajac84@yahoo.com</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://www.niebieski-tytan-group.pl</t>
+          <t>https://www.global-horyzont-group.pl</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Niebieski Uran SA</t>
+          <t>Future Oaza SA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Niebieski Uran</t>
+          <t>Future Oaza</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>84021439724</t>
+          <t>86021461729</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>izabela.rutkowska@gmail.com</t>
+          <t>izabela.pietrzak@gmail.com</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Niebieski Wektor S. A.</t>
+          <t>Wielkopolski Zefir S. A.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Niebieski Wektor</t>
+          <t>Wielkopolski Zefir</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>85032141114</t>
+          <t>87032163116</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>h.gorski@outlook.com</t>
+          <t>h.wojcicki@outlook.com</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>https://www.niebieski-wektor.eu</t>
+          <t>https://www.wielkopolski-zefir.eu</t>
         </is>
       </c>
     </row>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Niebieski Zefir Spółka Akcyjna</t>
+          <t>Śląski Pilica Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Niebieski Zefir</t>
+          <t>Śląski Pilica</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>86042842464</t>
+          <t>88042864466</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>sikora.weronika@wp.pl</t>
+          <t>czarnecka.weronika@wp.pl</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://niebieski-zefir.local</t>
+          <t>https://slaski-pilica.local</t>
         </is>
       </c>
     </row>
@@ -2614,12 +2614,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Niebieski Żubr sp. z o.o.</t>
+          <t>Mazowiecki Marmur sp. z o.o.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Niebieski Żubr</t>
+          <t>Mazowiecki Marmur</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>87050743857</t>
+          <t>89050765859</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>stanislawostrowski@onet.pl</t>
+          <t>stanislawlis@onetpl</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>https://www.niebieski-zubr-group.pl</t>
+          <t>https://www.mazowiecki-marmur-group.pl</t>
         </is>
       </c>
     </row>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Niebieski Sokół sp z oo</t>
+          <t>Pomorski Giewont sp z oo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Niebieski Sokół</t>
+          <t>Pomorski Giewont</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>88061445206</t>
+          <t>90061467207</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>zofia_tomaszewska@interia.pl</t>
+          <t>zofia_kolodziej@interia.pl</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>https://www.niebieski-sokol-group.com.pl</t>
+          <t>https://www.pomorski-giewont-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -2798,12 +2798,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Niebieski Orzeł sp. z o. o.</t>
+          <t>Dolnośląski Sudety sp. z o. o.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Niebieski Orzeł</t>
+          <t>Dolnośląski Sudety</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>89072146593</t>
+          <t>91072168594</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>bartlomiej.zajac90@o2.pl</t>
+          <t>bartlomiej.kaczmarek90@o2.pl</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>https://www.niebieski-orzel-group.eu</t>
+          <t>https://www.dolnoslaski-sudety-group.eu</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Niebieski Kormoran Sp. z o.o.</t>
+          <t>Karpacki Gryf Sp. z o.o.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Niebieski Kormoran</t>
+          <t>Karpacki Gryf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Niebieski Barycz SP Z O O</t>
+          <t>Bałtycki Neon SP Z O O</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Niebieski Barycz</t>
+          <t>Bałtycki Neon</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>d.sadowski@yahoocom</t>
+          <t>d.sadowski@yahoo.com</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>https://niebieski-barycz.pl</t>
+          <t>https://baltycki-neon.pl</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Niebieski Noteć spółka z ograniczoną odpowiedzialnością</t>
+          <t>Młody Wektor spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Niebieski Noteć</t>
+          <t>Młody Wektor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>https://www.niebieski-notec-group.com.pl</t>
+          <t>https://www.mlody-wektor-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -3166,12 +3166,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Niebieski Pilica Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wspólny Noteć Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Niebieski Pilica</t>
+          <t>Wspólny Noteć</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>https://www.niebieski-pilica-group.eu</t>
+          <t>https://www.wspolny-notec-group.eu</t>
         </is>
       </c>
     </row>
@@ -3258,12 +3258,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Niebieski Narew S.A.</t>
+          <t>Pierwszy Granit S.A.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Niebieski Narew</t>
+          <t>Pierwszy Granit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>https://www.niebieski-narew-group.local</t>
+          <t>https://www.pierwszy-granit-group.local</t>
         </is>
       </c>
     </row>
@@ -3350,12 +3350,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Niebieski Jodełka SA</t>
+          <t>Zielony Żubr SA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Niebieski Jodełka</t>
+          <t>Zielony Żubr</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://www.niebieski-jodelka.pl</t>
+          <t>https://www.zielony-zubr.pl</t>
         </is>
       </c>
     </row>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Niebieski Kaktus S. A.</t>
+          <t>Niebieski Narew S. A.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Niebieski Kaktus</t>
+          <t>Niebieski Narew</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Niebieski Szmaragd Spółka Akcyjna</t>
+          <t>Złoty Syrena Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Niebieski Szmaragd</t>
+          <t>Złoty Syrena</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://www.niebieski-szmaragd-group.eu</t>
+          <t>https://www.zloty-syrena-group.eu</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Niebieski Topaz sp. z o.o.</t>
+          <t>Srebrny Rysy sp. z o.o.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Niebieski Topaz</t>
+          <t>Srebrny Rysy</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>https://www.niebieski-topaz-group.local</t>
+          <t>https://www.srebrny-rysy-group.local</t>
         </is>
       </c>
     </row>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Niebieski Granit sp z oo</t>
+          <t>Czysty Amber sp z oo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Niebieski Granit</t>
+          <t>Czysty Amber</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>https://www.niebieski-granit-group.pl</t>
+          <t>https://www.czysty-amber-group.pl</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>zuzanna_wrobel.chmielewska@gmail.com</t>
+          <t>zuzanna_wrobel.chmielewska@finanse24.xs</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3902,12 +3902,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Niebieski Syrena Sp. z o.o.</t>
+          <t>Pewny Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Niebieski Syrena</t>
+          <t>Pewny Oaza</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>https://niebieski-syrena.eu</t>
+          <t>https://pewny-oaza.eu</t>
         </is>
       </c>
     </row>
@@ -3994,12 +3994,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Niebieski Zodiak SP Z O O</t>
+          <t>Dobry Zefir SP Z O O</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Niebieski Zodiak</t>
+          <t>Dobry Zefir</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Niebieski Olimp spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polski Pilica spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Niebieski Olimp</t>
+          <t>Polski Pilica</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>https://www.niebieski-olimp-group.pl</t>
+          <t>https://www.polski-pilica-group.pl</t>
         </is>
       </c>
     </row>
@@ -4178,12 +4178,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Niebieski Zorza Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Europejski Marmur Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Niebieski Zorza</t>
+          <t>Europejski Marmur</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>https://www.niebieski-zorza-group.com.pl</t>
+          <t>https://www.europejski-marmur-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Niebieski Krokus S.A.</t>
+          <t>Globalny Giewont S.A.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Niebieski Krokus</t>
+          <t>Globalny Giewont</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>https://www.niebieski-krokus.eu</t>
+          <t>https://www.globalny-giewont.eu</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Niebieski Narcyz SA</t>
+          <t>Lokalny Sudety SA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Niebieski Narcyz</t>
+          <t>Lokalny Sudety</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>https://niebieski-narcyz.local</t>
+          <t>https://lokalny-sudety.local</t>
         </is>
       </c>
     </row>
@@ -4454,12 +4454,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Niebieski Giewont S. A.</t>
+          <t>Nowoczesny Gryf S. A.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Niebieski Giewont</t>
+          <t>Nowoczesny Gryf</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>https://www.niebieski-giewont-group.pl</t>
+          <t>https://www.nowoczesny-gryf-group.pl</t>
         </is>
       </c>
     </row>
@@ -4546,12 +4546,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Niebieski Rysy Spółka Akcyjna</t>
+          <t>Tradycyjny Neon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Niebieski Rysy</t>
+          <t>Tradycyjny Neon</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Niebieski Kasprowy sp. z o.o.</t>
+          <t>Dynamiczny Wektor sp. z o.o.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Niebieski Kasprowy</t>
+          <t>Dynamiczny Wektor</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>m.wilk@finanse24.xs</t>
+          <t>m.wilk@outlook.com</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>https://www.niebieski-kasprowy-group.eu</t>
+          <t>https://www.dynamiczny-wektor-group.eu</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Amber Transport sp. z o. o.</t>
+          <t>Falcon Transport sp. z o. o.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Amber Transport</t>
+          <t>Falcon Transport</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>https://amber-transport.pl</t>
+          <t>https://falcon-transport.pl</t>
         </is>
       </c>
     </row>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Amber Spedycja Sp. z o.o.</t>
+          <t>Koral Spedycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Amber Spedycja</t>
+          <t>Koral Spedycja</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>https://www.amber-spedycja-group.com.pl</t>
+          <t>https://www.koral-spedycja-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -5006,12 +5006,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Amber Logistyka SP Z O O</t>
+          <t>Pegaz Logistyka SP Z O O</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Amber Logistyka</t>
+          <t>Pegaz Logistyka</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>https://www.amber-logistyka-group.eu</t>
+          <t>https://www.pegaz-logistyka-group.eu</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Amber Handel spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wektor Handel spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Amber Handel</t>
+          <t>Wektor Handel</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Amber Usługi Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Usługi Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Amber Usługi</t>
+          <t>Kormoran Usługi</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>https://www.amber-uslugi.pl</t>
+          <t>https://www.kormoran-uslugi.pl</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Amber Finanse S.A.</t>
+          <t>Jodełka Finanse S.A.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Amber Finanse</t>
+          <t>Jodełka Finanse</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>https://amber-finanse.com.pl</t>
+          <t>https://jodelka-finanse.com.pl</t>
         </is>
       </c>
     </row>
@@ -5374,12 +5374,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Amber Dorazdtwo SA</t>
+          <t>Marmur Doradztwo SA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Amber Doradztwo</t>
+          <t>Marmur Doradztwo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>https://www.amber-doradztwo-group.eu</t>
+          <t>https://www.marmur-doradztwo-group.eu</t>
         </is>
       </c>
     </row>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Amber Szkolenia S. A.</t>
+          <t>Krokus Szkolenia S. A.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Amber Szkolenia</t>
+          <t>Krokus Szkolenia</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>https://www.amber-szkolenia-group.local</t>
+          <t>https://www.krokus-szkolenia-group.local</t>
         </is>
       </c>
     </row>
@@ -5558,12 +5558,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Amber Media Spółka Akcyjna</t>
+          <t>Beskid Media Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Amber Media</t>
+          <t>Beskid Media</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>https://www.amber-media-group.pl</t>
+          <t>https://www.beskid-media-group.pl</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Amber Marketing sp z oo</t>
+          <t>Falcon Marketing sp z oo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Amber Marketing</t>
+          <t>Falcon Marketing</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>https://amber-marketing.eu</t>
+          <t>https://falcon-marketing.eu</t>
         </is>
       </c>
     </row>
@@ -5834,12 +5834,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Amber Druk sp. z o. o.</t>
+          <t>Koral Druk sp. z o. o.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Amber Druk</t>
+          <t>Koral Druk</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>https://www.amber-druk-group.local</t>
+          <t>https://www.koral-druk-group.local</t>
         </is>
       </c>
     </row>
@@ -5926,12 +5926,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Amber Informatyka Sp. z o.o.</t>
+          <t>Pegaz Informatyka Sp. z o.o.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Amber Informatyka</t>
+          <t>Pegaz Informatyka</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>https://www.amber-informatyka-group.pl</t>
+          <t>https://www.pegaz-informatyka-group.pl</t>
         </is>
       </c>
     </row>
@@ -6018,12 +6018,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Amber Oprogramowanie SP Z O O</t>
+          <t>Wektor Oprogramowanie SP Z O O</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Amber Oprogramowanie</t>
+          <t>Wektor Oprogramowanie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>https://www.amber-oprogramowanie-group.com.pl</t>
+          <t>https://www.wektor-oprogramowanie-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -6110,12 +6110,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Amber Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Amber Rolnictwo</t>
+          <t>Kormoran Rolnictwo</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>https://www.amber-rolnictwo.eu</t>
+          <t>https://www.kormoran-rolnictwo.eu</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Amber Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Amber Ogrodnictwo</t>
+          <t>Jodełka Ogrodnictwo</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Amber Produkcja S.A.</t>
+          <t>Marmur Produkcja S.A.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Amber Produkcja</t>
+          <t>Marmur Produkcja</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>https://www.amber-produkcja-group.pl</t>
+          <t>https://www.marmur-produkcja-group.pl</t>
         </is>
       </c>
     </row>
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Amber Przemysł SA</t>
+          <t>Krokus Przemysł SA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Amber Przemysł</t>
+          <t>Krokus Przemysł</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>https://www.amber-przemysl-group.com.pl</t>
+          <t>https://www.krokus-przemysl-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -6478,12 +6478,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Amber Ekologia S. A.</t>
+          <t>Beskid Ekologia S. A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Amber Ekologia</t>
+          <t>Beskid Ekologia</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>https://www.amber-ekologia-group.eu</t>
+          <t>https://www.beskid-ekologia-group.eu</t>
         </is>
       </c>
     </row>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Amber Instalacje sp. z o.o.</t>
+          <t>Falcon Instalacje sp. z o.o.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Amber Instalacje</t>
+          <t>Falcon Instalacje</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>https://amber-instalacje.pl</t>
+          <t>https://falcon-instalacje.pl</t>
         </is>
       </c>
     </row>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Amber Nieruchomości sp z oo</t>
+          <t>Koral Nieruchomości sp z oo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Amber Nieruchomości</t>
+          <t>Koral Nieruchomości</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Amber Inwestycje sp. z o. o.</t>
+          <t>Pegaz Inwestycje sp. z o. o.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Amber Inwestycje</t>
+          <t>Pegaz Inwestycje</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>https://www.amber-inwestycje-group.eu</t>
+          <t>https://www.pegaz-inwestycje-group.eu</t>
         </is>
       </c>
     </row>
@@ -6938,12 +6938,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Amber Medycyna Sp. z o.o.</t>
+          <t>Wektor Medycyna Sp. z o.o.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Amber Medycyna</t>
+          <t>Wektor Medycyna</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>https://www.amber-medycyna-group.local</t>
+          <t>https://www.wektor-medycyna-group.local</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Amber Zdrowie SP Z O O</t>
+          <t>Kormoran Zdrowie SP Z O O</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Amber Zdrowie</t>
+          <t>Kormoran Zdrowie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>https://www.amber-zdrowie.pl</t>
+          <t>https://www.kormoran-zdrowie.pl</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Amber Urody spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Urody spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Amber Urody</t>
+          <t>Jodełka Urody</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>https://amber-urody.com.pl</t>
+          <t>https://jodelka-urody.com.pl</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Amber Turystyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Turystyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Amber Turystyka</t>
+          <t>Marmur Turystyka</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>https://www.amber-turystyka-group.eu</t>
+          <t>https://www.marmur-turystyka-group.eu</t>
         </is>
       </c>
     </row>
@@ -7306,12 +7306,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Amber Rozrywka S.A.</t>
+          <t>Krokus Rozrywka S.A.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Amber Rozrywka</t>
+          <t>Krokus Rozrywka</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Amber Gastronomia SA</t>
+          <t>Beskid Gastronomia SA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Amber Gastronomia</t>
+          <t>Beskid Gastronomia</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>https://www.amber-gastronomia-group.pl</t>
+          <t>https://www.beskid-gastronomia-group.pl</t>
         </is>
       </c>
     </row>
@@ -7582,12 +7582,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Amber Tekstylia Spółka Akcyjna</t>
+          <t>Falcon Tekstylia Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Amber Tekstylia</t>
+          <t>Falcon Tekstylia</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>https://amber-tekstylia.eu</t>
+          <t>https://falcon-tekstylia.eu</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Amber Motoryzacja sp. z o.o.</t>
+          <t>Koral Motoryzacja sp. z o.o.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Amber Motoryzacja</t>
+          <t/>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t/>
+          <t>ulica Kościuszki 75, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>https://www.amber-motoryzacja-group.local</t>
+          <t>https://www.koral-motoryzacja-group.local</t>
         </is>
       </c>
     </row>
@@ -7766,12 +7766,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Amber Ubezpieczenia sp z oo</t>
+          <t>Pegaz Ubezpieczenia sp z oo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Amber Ubezpieczenia</t>
+          <t>Pegaz Ubezpieczenia</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>https://www.amber-ubezpieczenia-group.pl</t>
+          <t>https://www.pegaz-ubezpieczenia-group.pl</t>
         </is>
       </c>
     </row>
@@ -7858,12 +7858,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Amber Spawalnictwo sp. z o. o.</t>
+          <t>Wektor Spawalnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Amber Spawalnictwo</t>
+          <t>Wektor Spawalnictwo</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Amber Ślusarstwo Sp. z o.o.</t>
+          <t>Kormoran Ślusarstwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Amber Ślusarstwo</t>
+          <t>Kormoran Ślusarstwo</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>https://www.amber-slusarstwo.eu</t>
+          <t>https://www.kormoran-slusarstwo.eu</t>
         </is>
       </c>
     </row>
@@ -8042,12 +8042,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Amber Krawiectwo SP Z O O</t>
+          <t>Jodełka Krawiectwo SP Z O O</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Amber Krawiectwo</t>
+          <t>Jodełka Krawiectwo</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1289129807</t>
+          <t/>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>https://amber-krawiectwo.local</t>
+          <t>https://jodelka-krawiectwo.local</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Amber Ochrona spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Ochrona spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Amber Ochrona</t>
+          <t>Marmur Ochrona</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>https://www.amber-ochrona-group.pl</t>
+          <t>https://www.marmur-ochrona-group.pl</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Amber Catering Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Krokus Catering Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Amber Catering</t>
+          <t>Krokus Catering</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t/>
+          <t>1299288217</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>https://www.amber-catering-group.com.pl</t>
+          <t>https://www.krokus-catering-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -8318,12 +8318,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Amber Księgowość S.A.</t>
+          <t>Beskid Księgowość S.A.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Amber Księgowość</t>
+          <t>Beskid Księgowość</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>bartlomiej.biernat92@outlook.com</t>
+          <t>bartlomiej.biernat92@ubezpiecznia.pl</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>https://www.amber-ksiegowosc-group.eu</t>
+          <t>https://www.beskid-ksiegowosc-group.eu</t>
         </is>
       </c>
     </row>
@@ -8410,12 +8410,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bizon Budownictwo SA</t>
+          <t>Jantar Budownictwo SA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bizon Budownictwo</t>
+          <t>Jantar Budownictwo</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bizon Transport S. A.</t>
+          <t>Oaza Transport S. A.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bizon Transport</t>
+          <t>Oaza Transport</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>https://bizon-transport.pl</t>
+          <t>https://oaza-transport.pl</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bizon Spedycja Spółka Akcyjna</t>
+          <t>Uran Spedycja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bizon Spedycja</t>
+          <t>Uran Spedycja</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>https://www.bizon-spedycja-group.com.pl</t>
+          <t>https://www.uran-spedycja-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -8686,12 +8686,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bizon Logistyka sp. z o.o.</t>
+          <t>Orzeł Logistyka sp. z o.o.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bizon Logistyka</t>
+          <t>Orzeł Logistyka</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>https://www.bizon-logistyka-group.eu</t>
+          <t>https://www.orzel-logistyka-group.eu</t>
         </is>
       </c>
     </row>
@@ -8778,12 +8778,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bizon Handel sp z oo</t>
+          <t>Narew Handel sp z oo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bizon Handel</t>
+          <t>Narew Handel</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>https://www.bizon-handel-group.local</t>
+          <t>https://www.narew-handel-group.local</t>
         </is>
       </c>
     </row>
@@ -8870,12 +8870,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bizon Usługi sp. z o. o.</t>
+          <t>Granit Usługi sp. z o. o.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bizon Usługi</t>
+          <t>Granit Usługi</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>https://www.bizon-uslugi.pl</t>
+          <t>https://www.granit-uslugi.pl</t>
         </is>
       </c>
     </row>
@@ -8962,12 +8962,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bizon Finanse Sp. z o.o.</t>
+          <t>Zorza Finanse Sp. z o.o.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bizon Finanse</t>
+          <t>Zorza Finanse</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -9054,12 +9054,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bizon Doradztwo SP Z O O</t>
+          <t>Kasprowy Doradztwo SP Z O O</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bizon Doradztwo</t>
+          <t>Kasprowy Doradztwo</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>https://www.bizon-doradztwo-group.eu</t>
+          <t>https://www.kasprowy-doradztwo-group.eu</t>
         </is>
       </c>
     </row>
@@ -9146,12 +9146,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bizon Szkolenia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sudety Szkolenia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bizon Szkolenia</t>
+          <t>Sudety Szkolenia</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>https://www.bizon-szkolenia-group.local</t>
+          <t>https://www.sudety-szkolenia-group.local</t>
         </is>
       </c>
     </row>
@@ -9238,12 +9238,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bizon Media Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Media Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bizon Media</t>
+          <t>Echo Media</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>filiplewandowski@ubezpiecznia.pl</t>
+          <t>filiplewandowski@onet.pl</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>https://www.bizon-media-group.pl</t>
+          <t>https://www.echo-media-group.pl</t>
         </is>
       </c>
     </row>
@@ -9330,12 +9330,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>P.P.H.U. Bizon Reklama</t>
+          <t>P.P.H.U. Jantar Reklama</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>P.P.H.U. Bizon Reklama</t>
+          <t>P.P.H.U. Jantar Reklama</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>https://www.bizon-reklama.com.pl</t>
+          <t>https://www.jantar-reklama.com.pl</t>
         </is>
       </c>
     </row>
@@ -9422,12 +9422,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bizon Marketing SA</t>
+          <t>Oaza Marketing SA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bizon Marketing</t>
+          <t>Oaza Marketing</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>https://bizon-marketing.eu</t>
+          <t>https://oaza-marketing.eu</t>
         </is>
       </c>
     </row>
@@ -9514,12 +9514,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Bizon Druk S. A.</t>
+          <t>Uran Druk S. A.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bizon Druk</t>
+          <t>Uran Druk</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bizon Informatyka Spółka Akcyjna</t>
+          <t>Orzeł Informatyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bizon Informatyka</t>
+          <t>Orzeł Informatyka</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>https://www.bizon-informatyka-group.pl</t>
+          <t>https://www.orzel-informatyka-group.pl</t>
         </is>
       </c>
     </row>
@@ -9698,12 +9698,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Bizon Oprogramowanie sp. z o.o.</t>
+          <t>Narew Oprogramowanie sp. z o.o.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bizon Oprogramowanie</t>
+          <t>Narew Oprogramowanie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>https://www.bizon-oprogramowanie-group.com.pl</t>
+          <t>https://www.narew-oprogramowanie-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -9790,12 +9790,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Bizon Rolnictwo sp z oo</t>
+          <t>Granit Rolnictwo sp z oo</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bizon Rolnictwo</t>
+          <t>Granit Rolnictwo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>https://www.bizon-rolnictwo.eu</t>
+          <t>https://www.granit-rolnictwo.eu</t>
         </is>
       </c>
     </row>
@@ -9882,12 +9882,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bizon Ogrodnictwo sp. z o. o.</t>
+          <t>Zorza Ogrodnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bizon Ogrodnictwo</t>
+          <t>Zorza Ogrodnictwo</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>https://bizon-ogrodnictwo.local</t>
+          <t>https://zorza-ogrodnictwo.local</t>
         </is>
       </c>
     </row>
@@ -9974,12 +9974,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bizon Produkcja pS. z o.o.</t>
+          <t>Kasprowy Produkcja Sp. z o.o.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bizon Produkcja</t>
+          <t>Kasprowy Produkcja</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Graboswki</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>https://www.bizon-produkcja-group.pl</t>
+          <t>https://www.kasprowy-produkcja-group.pl</t>
         </is>
       </c>
     </row>
@@ -10066,12 +10066,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bizon Przemysł SP Z O O</t>
+          <t>Sudety Przemysł SP Z O O</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bizon Przemysł</t>
+          <t>Sudety Przemysł</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bizon Ekologia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Ekologia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bizon Ekologia</t>
+          <t>Echo Ekologia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>https://www.bizon-ekologia-group.eu</t>
+          <t>https://www.echo-ekologia-group.eu</t>
         </is>
       </c>
     </row>
@@ -10250,12 +10250,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bizon Energetyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jantar Energetyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bizon Energetyka</t>
+          <t>Jantar Energetyka</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>https://www.bizon-energetyka.local</t>
+          <t>https://www.jantar-energetyka.local</t>
         </is>
       </c>
     </row>
@@ -10342,12 +10342,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bizon Instalacje S.A.</t>
+          <t>Oaza Instalacje S.A.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bizon Instalacje</t>
+          <t>Oaza Instalacje</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>https://bizon-instalacje.pl</t>
+          <t>https://oaza-instalacje.pl</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Bizon Nieruchomości SA</t>
+          <t>Uran Nieruchomości SA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bizon Nieruchomości</t>
+          <t>Uran Nieruchomości</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>https://www.bizon-nieruchomosci-group.com.pl</t>
+          <t>https://www.uran-nieruchomosci-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -10526,12 +10526,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Bizon Inwestycje S. A.</t>
+          <t>Orzeł Inwestycje S. A.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bizon Inwestycje</t>
+          <t>Orzeł Inwestycje</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>83072183675</t>
+          <t>93072183675</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>https://www.bizon-inwestycje-group.eu</t>
+          <t>https://www.orzel-inwestycje-group.eu</t>
         </is>
       </c>
     </row>
@@ -10618,12 +10618,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bizon Medycyna Spółka Akcyjna</t>
+          <t>Narew Medycyna Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bizon Medycyna</t>
+          <t>Narew Medycyna</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bizon Zdrowie sp. z o.o.</t>
+          <t>Granit Zdrowie sp. z o.o.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bizon Zdrowie</t>
+          <t>Granit Zdrowie</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>95090786418</t>
+          <t>85090786418</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -10790,7 +10790,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>https://www.bizon-zdrowie.pl</t>
+          <t>https://www.granit-zdrowie.pl</t>
         </is>
       </c>
     </row>
@@ -10802,12 +10802,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bizon Urody sp z oo</t>
+          <t>Zorza Urody sp z oo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bizon Urody</t>
+          <t>Zorza Urody</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>https://bizon-urody.com.pl</t>
+          <t>https://zorza-urody.com.pl</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Bizon Turystyka sp. z o. o.</t>
+          <t>Kasprowy Turystyka sp. z o. o.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bizon Turystyka</t>
+          <t>Kasprowy Turystyka</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>https://www.bizon-turystyka-group.eu</t>
+          <t>https://www.kasprowy-turystyka-group.eu</t>
         </is>
       </c>
     </row>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Bizon Rozrywka Sp. z o.o.</t>
+          <t>Sudety Rozrywka Sp. z o.o.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bizon Rozrywka</t>
+          <t>Sudety Rozrywka</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>https://www.bizon-rozrywka-group.local</t>
+          <t>https://www.sudety-rozrywka-group.local</t>
         </is>
       </c>
     </row>
@@ -11078,12 +11078,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Bizon Gastronomia SP Z O O</t>
+          <t>Echo Gastronomia SP Z O O</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bizon Gastronomia</t>
+          <t>Echo Gastronomia</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>https://www.bizon-gastronomia-group.pl</t>
+          <t>https://www.echo-gastronomia-group.pl</t>
         </is>
       </c>
     </row>
@@ -11262,12 +11262,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Bizon Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Oaza Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bizon Tekstylia</t>
+          <t>Oaza Tekstylia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -11342,7 +11342,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>https://bizon-tekstylia.eu</t>
+          <t>https://oaza-tekstylia.eu</t>
         </is>
       </c>
     </row>
@@ -11354,12 +11354,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bizon Motoryzacja S.A.</t>
+          <t>Uran Motoryzacja S.A.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bizon Motoryzacja</t>
+          <t>Uran Motoryzacja</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>https://www.bizon-motoryzacja-group.local</t>
+          <t>https://www.uran-motoryzacja-group.local</t>
         </is>
       </c>
     </row>
@@ -11446,12 +11446,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bizon Ubezpieczenia SA</t>
+          <t>Orzeł Ubezpieczenia SA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bizon Ubezpieczenia</t>
+          <t>Orzeł Ubezpieczenia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>https://www.bizon-ubezpieczenia-group.pl</t>
+          <t>https://www.orzel-ubezpieczenia-group.pl</t>
         </is>
       </c>
     </row>
@@ -11538,12 +11538,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Bizon Spawalnictwo S. A.</t>
+          <t>Narew Spawalnictwo S. A.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bizon Spawalnictwo</t>
+          <t>Narew Spawalnictwo</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>https://www.bizon-spawalnictwo-group.com.pl</t>
+          <t>https://www.narew-spawalnictwo-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -11630,12 +11630,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Bizon Ślusarstwo Spółka Akcyjna</t>
+          <t>Granit Ślusarstwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bizon Ślusarstwo</t>
+          <t>Granit Ślusarstwo</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>1292218219</t>
+          <t>2292218219</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>https://www.bizon-slusarstwo.eu</t>
+          <t>https://www.granit-slusarstwo.eu</t>
         </is>
       </c>
     </row>
@@ -11722,12 +11722,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bizon Krawiectwo sp. z o.o.</t>
+          <t>Zorza Krawiectwo sp. z o.o.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bizon Krawiectwo</t>
+          <t>Zorza Krawiectwo</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>monika.lis@proton.me</t>
+          <t>monika.lisproton.me</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11814,12 +11814,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bizon Ochrona sp z oo</t>
+          <t>Kasprowy Ochrona sp z oo</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bizon Ochrona</t>
+          <t>Kasprowy Ochrona</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2292376591</t>
+          <t>1292376591</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>https://www.bizon-ochrona-group.pl</t>
+          <t>https://www.kasprowy-ochrona-group.pl</t>
         </is>
       </c>
     </row>
@@ -11906,12 +11906,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bizon Catering sp. z o. o.</t>
+          <t>Sudety Catering sp. z o. o.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bizon Catering</t>
+          <t>Sudety Catering</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>https://www.bizon-catering-group.com.pl</t>
+          <t>https://www.sudety-catering-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bizon Księgowość Sp. z o.o.</t>
+          <t>Echo Księgowość Sp. z o.o.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bizon Księgowość</t>
+          <t>Echo Księgowość</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>https://www.bizon-ksiegowosc-group.eu</t>
+          <t>https://www.echo-ksiegowosc-group.eu</t>
         </is>
       </c>
     </row>
@@ -12090,12 +12090,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Canyon Budownictwo SP Z O O</t>
+          <t>Tytan Budownictwo SP Z O O</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Canyon Budownictwo</t>
+          <t>Tytan Budownictwo</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>https://www.canyon-budownictwo.local</t>
+          <t>https://www.tytan-budownictwo.local</t>
         </is>
       </c>
     </row>
@@ -12182,12 +12182,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Canyon Transport spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sokół Transport spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Canyon Transport</t>
+          <t>Sokół Transport</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>andrzej.wlodarczyk76onet.pl</t>
+          <t>andrzej.wlodarczyk76@onet.pl</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>https://canyon-transport.pl</t>
+          <t>https://sokol-transport.pl</t>
         </is>
       </c>
     </row>
@@ -12274,12 +12274,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Canyon Spedycja Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Spedycja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Canyon Spedycja</t>
+          <t>Pilica Spedycja</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Canyon Logistyka S.A.</t>
+          <t>Topaz Logistyka S.A.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Canyon Logistyka</t>
+          <t>Topaz Logistyka</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>https://www.canyon-logistyka-group.eu</t>
+          <t>https://www.topaz-logistyka-group.eu</t>
         </is>
       </c>
     </row>
@@ -12458,12 +12458,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Canyon Handel SA</t>
+          <t>Olimp Handel SA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Canyon Handel</t>
+          <t>Olimp Handel</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>https://www.canyon-handel-group.local</t>
+          <t>https://www.olimp-handel-group.local</t>
         </is>
       </c>
     </row>
@@ -12550,12 +12550,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Canyon Usługi S. A.</t>
+          <t>Rysy Usługi S. A.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Canyon Usługi</t>
+          <t>Rysy Usługi</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>https://www.canyon-uslugi.pl</t>
+          <t>https://www.rysy-uslugi.pl</t>
         </is>
       </c>
     </row>
@@ -12642,12 +12642,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Canyon Finanse Spółka Akcyjna</t>
+          <t>Bałtyk Finanse Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Canyon Finanse</t>
+          <t>Bałtyk Finanse</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>https://canyon-finanse.com.pl</t>
+          <t>https://baltyk-finanse.com.pl</t>
         </is>
       </c>
     </row>
@@ -12734,12 +12734,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Canyon Doradztwo sp. z o.o.</t>
+          <t>Delfin Doradztwo sp. z o.o.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Canyon Doradztwo</t>
+          <t>Delfin Doradztwo</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>https://www.canyon-doradztwo-group.eu</t>
+          <t>https://www.delfin-doradztwo-group.eu</t>
         </is>
       </c>
     </row>
@@ -12826,12 +12826,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Canyon Szkolenia sp z oo</t>
+          <t>Ikar Szkolenia sp z oo</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Canyon Szkolenia</t>
+          <t>Ikar Szkolenia</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>dorota.sokolowska@wp.pl</t>
+          <t>dorota.sokolowska@abxza.pl</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12918,12 +12918,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Canyon Media sp. z o. o.</t>
+          <t>Neon Media sp. z o. o.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Canyon Media</t>
+          <t>Neon Media</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>https://www.canyon-media-group.pl</t>
+          <t>https://www.neon-media-group.pl</t>
         </is>
       </c>
     </row>
@@ -13010,12 +13010,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PPHU Canyon Reklama</t>
+          <t>PPHU Tytan Reklama</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PPHU Canyon Reklama</t>
+          <t>PPHU Tytan Reklama</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>https://www.canyon-reklama.com.pl</t>
+          <t>https://www.tytan-reklama.com.pl</t>
         </is>
       </c>
     </row>
@@ -13102,12 +13102,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Canyon Marketing SP Z O O</t>
+          <t>Sokół Marketing SP Z O O</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Canyon Marketing</t>
+          <t>Sokół Marketing</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>https://canyon-marketing.eu</t>
+          <t>https://sokol-marketing.eu</t>
         </is>
       </c>
     </row>
@@ -13194,12 +13194,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Canyon Druk spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Druk spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Canyon Druk</t>
+          <t>Pilica Druk</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>https://www.canyon-druk-group.local</t>
+          <t>https://www.pilica-druk-group.local</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Canyon Informatyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Informatyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Canyon Informatyka</t>
+          <t>Topaz Informatyka</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>https://www.canyon-informatyka-group.pl</t>
+          <t>https://www.topaz-informatyka-group.pl</t>
         </is>
       </c>
     </row>
@@ -13378,12 +13378,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Canyon Oprogramowanie S.A.</t>
+          <t>Olimp Oprogramowanie S.A.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Canyon Oprogramowanie</t>
+          <t>Olimp Oprogramowanie</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Canyon Rolnictwo SA</t>
+          <t>Rysy Rolnictwo SA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Canyon Rolnictwo</t>
+          <t>Rysy Rolnictwo</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>https://www.canyon-rolnictwo.eu</t>
+          <t>https://www.rysy-rolnictwo.eu</t>
         </is>
       </c>
     </row>
@@ -13562,12 +13562,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Canyon Ogrodnictwo S. A.</t>
+          <t>Bałtyk Ogrodnictwo S. A.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Canyon Ogrodnictwo</t>
+          <t>Bałtyk Ogrodnictwo</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13642,7 +13642,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>https://canyon-ogrodnictwo.local</t>
+          <t>https://baltyk-ogrodnictwo.local</t>
         </is>
       </c>
     </row>
@@ -13654,12 +13654,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Canyon Produkcja Spółka Akcyjna</t>
+          <t>Delfin Produkcja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Canyon Produkcja</t>
+          <t>Delfin Produkcja</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>https://www.canyon-produkcja-group.pl</t>
+          <t>https://www.delfin-produkcja-group.pl</t>
         </is>
       </c>
     </row>
@@ -13746,12 +13746,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Canyon Przemysł sp. z o.o.</t>
+          <t>Ikar Przemysł sp. z o.o.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Canyon Przemysł</t>
+          <t>Ikar Przemysł</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>https://www.canyon-przemysl-group.com.pl</t>
+          <t>https://www.ikar-przemysl-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -13838,12 +13838,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Canyon Ekologia sp z oo</t>
+          <t>Neon Ekologia sp z oo</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Canyon Ekologia</t>
+          <t>Neon Ekologia</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>bartlomiej.wysocki94@abxza.pl</t>
+          <t>bartlomiej.wysocki94@o2.pl</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>https://www.canyon-ekologia-group.eu</t>
+          <t>https://www.neon-ekologia-group.eu</t>
         </is>
       </c>
     </row>
@@ -13930,12 +13930,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Canyon Energetyka sp. z o. o.</t>
+          <t>Tytan Energetyka sp. z o. o.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Canyon Energetyka</t>
+          <t>Tytan Energetyka</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>70.22.Z</t>
+          <t/>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -14022,12 +14022,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Canyon Instalacje Sp. z o.o.</t>
+          <t>Sokół Instalacje Sp. z o.o.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Canyon Instalacje</t>
+          <t>Sokół Instalacje</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>https://canyon-instalacje.pl</t>
+          <t>https://sokol-instalacje.pl</t>
         </is>
       </c>
     </row>
@@ -14114,12 +14114,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Canyon Nieruchomości SP Z O O</t>
+          <t>Pilica Nieruchomości SP Z O O</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Canyon Nieruchomości</t>
+          <t>Pilica Nieruchomości</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>https://www.canyon-nieruchomosci-group.com.pl</t>
+          <t>https://www.pilica-nieruchomosci-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Canyon Inwestycje spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Inwestycje spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Canyon Inwestycje</t>
+          <t>Topaz Inwestycje</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -14286,7 +14286,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>https://www.canyon-inwestycje-group.eu</t>
+          <t>https://www.topaz-inwestycje-group.eu</t>
         </is>
       </c>
     </row>
@@ -14298,12 +14298,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Canyon Medycyna Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Medycyna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Canyon Medycyna</t>
+          <t>Olimp Medycyna</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>https://www.canyon-medycyna-group.local</t>
+          <t>https://www.olimp-medycyna-group.local</t>
         </is>
       </c>
     </row>
@@ -14390,12 +14390,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Canyon Zdrowie S.A.</t>
+          <t>Rysy Zdrowie S.A.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Canyon Zdrowie</t>
+          <t>Rysy Zdrowie</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>https://www.canyon-zdrowie.pl</t>
+          <t>https://www.rysy-zdrowie.pl</t>
         </is>
       </c>
     </row>
@@ -14482,12 +14482,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Canyon Urody SA</t>
+          <t>Bałtyk Urody SA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Canyon Urody</t>
+          <t>Bałtyk Urody</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -14574,17 +14574,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Canyon Turystyka S. A.</t>
+          <t>Delfin Turystyka S. A.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Canyon Tuyrstyka</t>
+          <t>Delfin Turystyka</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Cezary</t>
+          <t>Czeary</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>https://www.canyon-turystyka-group.eu</t>
+          <t>https://www.delfin-turystyka-group.eu</t>
         </is>
       </c>
     </row>
@@ -14666,12 +14666,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Canyon Rozrywka Spółka Akcyjna</t>
+          <t>Ikar Rozrywka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Canyon Rozrywka</t>
+          <t>Ikar Rozrywka</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>https://www.canyon-rozrywka-group.local</t>
+          <t>https://www.ikar-rozrywka-group.local</t>
         </is>
       </c>
     </row>
@@ -14758,12 +14758,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Canyon Gastronomia sp. z o.o.</t>
+          <t>Neon Gastronomia sp. z o.o.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Canyon Gastronomia</t>
+          <t>Neon Gastronomia</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>https://www.canyon-gastronomia-group.pl</t>
+          <t>https://www.neon-gastronomia-group.pl</t>
         </is>
       </c>
     </row>
@@ -14942,12 +14942,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Canyon Tekstylia sp. z o. o.</t>
+          <t>Sokół Tekstylia sp. z o. o.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Canyon Tekstylia</t>
+          <t>Sokół Tekstylia</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>https://canyon-tekstylia.eu</t>
+          <t>https://sokol-tekstylia.eu</t>
         </is>
       </c>
     </row>
@@ -15034,12 +15034,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Canyon Motoryzacja Sp. z o.o.</t>
+          <t>Pilica Motoryzacja Sp. z o.o.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Canyon Motoryzacja</t>
+          <t>Pilica Motoryzacja</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Canyon Ubezpieczenia SP Z O O</t>
+          <t>Topaz Ubezpieczenia SP Z O O</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Canyon Ubezpieczenia</t>
+          <t>Topaz Ubezpieczenia</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>https://www.canyon-ubezpieczenia-group.pl</t>
+          <t>https://www.topaz-ubezpieczenia-group.pl</t>
         </is>
       </c>
     </row>
@@ -15218,12 +15218,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Canyon Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Canyon Spawalnictwo</t>
+          <t>Olimp Spawalnictwo</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>https://www.canyon-spawalnictwo-group.com.pl</t>
+          <t>https://www.olimp-spawalnictwo-group.com.pl</t>
         </is>
       </c>
     </row>
@@ -15310,12 +15310,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Canyon Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Rysy Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Canyon Ślusarstwo</t>
+          <t>Rysy Ślusarstwo</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>https://www.canyon-slusarstwo.eu</t>
+          <t>https://www.rysy-slusarstwo.eu</t>
         </is>
       </c>
     </row>
@@ -15402,12 +15402,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Canyon Krawiectwo S.A.</t>
+          <t>Bałtyk Krawiectwo S.A.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Canyon Krawiectwo</t>
+          <t>Bałtyk Krawiectwo</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>https://canyon-krawiectwo.local</t>
+          <t>https://baltyk-krawiectwo.local</t>
         </is>
       </c>
     </row>
@@ -15494,12 +15494,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Canyon Ochrona SA</t>
+          <t>Delfin Ochrona SA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Canyon Ochrona</t>
+          <t>Delfin Ochrona</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>https://www.canyon-ochrona-group.pl</t>
+          <t>https://www.delfin-ochrona-group.pl</t>
         </is>
       </c>
     </row>
@@ -15586,12 +15586,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Canyon Catering S. A.</t>
+          <t>Ikar Catering S. A.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Canyon Catering</t>
+          <t>Ikar Catering</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -15678,12 +15678,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Canyon Księgowość Spółka Akcyjna</t>
+          <t>Neon Księgowość Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Canyon Księgowość</t>
+          <t>Neon Księgowość</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>https://www.canyon-ksiegowosc-group.eu</t>
+          <t>https://www.neon-ksiegowosc-group.eu</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>m.czajkowski@onet.pl</t>
+          <t>m.czajkowski@uuu.xs</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>d.zielinski@uuu.xs</t>
+          <t>d.zielinski@yahoo.com</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
